--- a/dados.xlsx
+++ b/dados.xlsx
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1813" uniqueCount="1813">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1867" uniqueCount="1867">
   <si>
     <t>CPF</t>
   </si>
@@ -5466,6 +5466,168 @@
   </si>
   <si>
     <t>77lpyci</t>
+  </si>
+  <si>
+    <t>010101024096</t>
+  </si>
+  <si>
+    <t>010101023341</t>
+  </si>
+  <si>
+    <t>010101036707</t>
+  </si>
+  <si>
+    <t>010101023352</t>
+  </si>
+  <si>
+    <t>010101020947</t>
+  </si>
+  <si>
+    <t>010101030288</t>
+  </si>
+  <si>
+    <t>010101034654</t>
+  </si>
+  <si>
+    <t>010101023775</t>
+  </si>
+  <si>
+    <t>010101028392</t>
+  </si>
+  <si>
+    <t>010101023408</t>
+  </si>
+  <si>
+    <t>010101034584</t>
+  </si>
+  <si>
+    <t>010101033618</t>
+  </si>
+  <si>
+    <t>010101023659</t>
+  </si>
+  <si>
+    <t>010101040353</t>
+  </si>
+  <si>
+    <t>010101026603</t>
+  </si>
+  <si>
+    <t>010101040772</t>
+  </si>
+  <si>
+    <t>010101023369</t>
+  </si>
+  <si>
+    <t>010101023354</t>
+  </si>
+  <si>
+    <t>hrs73l8</t>
+  </si>
+  <si>
+    <t>abtxmwk</t>
+  </si>
+  <si>
+    <t>h62vv7b</t>
+  </si>
+  <si>
+    <t>6dusnab</t>
+  </si>
+  <si>
+    <t>y4h6knf</t>
+  </si>
+  <si>
+    <t>lefjl9j</t>
+  </si>
+  <si>
+    <t>19sff78</t>
+  </si>
+  <si>
+    <t>luvb702</t>
+  </si>
+  <si>
+    <t>rjfy1ki</t>
+  </si>
+  <si>
+    <t>5iqkszk</t>
+  </si>
+  <si>
+    <t>jkiyhve</t>
+  </si>
+  <si>
+    <t>oe3nx4p</t>
+  </si>
+  <si>
+    <t>dmgq1yz</t>
+  </si>
+  <si>
+    <t>kbcl15k</t>
+  </si>
+  <si>
+    <t>0uavjvu</t>
+  </si>
+  <si>
+    <t>rbhx7kv</t>
+  </si>
+  <si>
+    <t>jtqda50</t>
+  </si>
+  <si>
+    <t>7f7f5jk</t>
+  </si>
+  <si>
+    <t>ANA LUCIA FERREIRA DA COSTA</t>
+  </si>
+  <si>
+    <t>ANGELA MARIA FIDELIS DA SILVA</t>
+  </si>
+  <si>
+    <t>CARLA REGINA BELO CESARINO</t>
+  </si>
+  <si>
+    <t>ELIANE DA CUNHA VASCONCELLOS</t>
+  </si>
+  <si>
+    <t>GARDENIA BARROS DO AMARANTE</t>
+  </si>
+  <si>
+    <t>IARA FERNANDES ABREU</t>
+  </si>
+  <si>
+    <t>JOELMA LOBO DE FARIA</t>
+  </si>
+  <si>
+    <t>LUCIANA VICENTE FERREIRA</t>
+  </si>
+  <si>
+    <t>MARCIA CRISTINA ALVES DA COSTA</t>
+  </si>
+  <si>
+    <t>MARCOS AURELIO DE OLIVEIRA</t>
+  </si>
+  <si>
+    <t>MARIA DE FATIMA RODRIGUES LEANDRO</t>
+  </si>
+  <si>
+    <t>ODNISSE ALVES BARBOSA DE SOUSA</t>
+  </si>
+  <si>
+    <t>PATRICIA APARECIDA ALVES DOS ANJOS</t>
+  </si>
+  <si>
+    <t>POLIANE FERNANDA FIDELIS BENVINDO</t>
+  </si>
+  <si>
+    <t>ROSANGELA TEREZINHA LINO</t>
+  </si>
+  <si>
+    <t>SANDRA DA SILVA GELLER</t>
+  </si>
+  <si>
+    <t>SANDRA FERREIRA DE MOURA</t>
+  </si>
+  <si>
+    <t>VIVIANE APARECIDA DOS SANTOS</t>
   </si>
 </sst>
 </file>
@@ -5788,7 +5950,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:D604"/>
+  <dimension ref="A1:D622"/>
   <sheetFormatPr defaultRowHeight="15.75" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="13.625" style="1" bestFit="1" customWidth="1"/>
@@ -14254,6 +14416,258 @@
         <v>1812</v>
       </c>
     </row>
+    <row r="605" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A605" s="1">
+        <v>12213421854</v>
+      </c>
+      <c r="B605" s="2" t="s">
+        <v>1849</v>
+      </c>
+      <c r="C605" s="2" t="s">
+        <v>1813</v>
+      </c>
+      <c r="D605" t="s">
+        <v>1831</v>
+      </c>
+    </row>
+    <row r="606" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A606" s="1">
+        <v>12946369870</v>
+      </c>
+      <c r="B606" s="2" t="s">
+        <v>1850</v>
+      </c>
+      <c r="C606" s="2" t="s">
+        <v>1814</v>
+      </c>
+      <c r="D606" t="s">
+        <v>1832</v>
+      </c>
+    </row>
+    <row r="607" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A607" s="1">
+        <v>41866731874</v>
+      </c>
+      <c r="B607" s="2" t="s">
+        <v>1851</v>
+      </c>
+      <c r="C607" s="2" t="s">
+        <v>1815</v>
+      </c>
+      <c r="D607" t="s">
+        <v>1833</v>
+      </c>
+    </row>
+    <row r="608" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A608" s="1">
+        <v>30579044831</v>
+      </c>
+      <c r="B608" s="2" t="s">
+        <v>1852</v>
+      </c>
+      <c r="C608" s="2" t="s">
+        <v>1816</v>
+      </c>
+      <c r="D608" t="s">
+        <v>1834</v>
+      </c>
+    </row>
+    <row r="609" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A609" s="1">
+        <v>35504818885</v>
+      </c>
+      <c r="B609" s="2" t="s">
+        <v>1853</v>
+      </c>
+      <c r="C609" s="2" t="s">
+        <v>1817</v>
+      </c>
+      <c r="D609" t="s">
+        <v>1835</v>
+      </c>
+    </row>
+    <row r="610" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A610" s="1">
+        <v>41612487840</v>
+      </c>
+      <c r="B610" s="2" t="s">
+        <v>1854</v>
+      </c>
+      <c r="C610" s="2" t="s">
+        <v>1818</v>
+      </c>
+      <c r="D610" t="s">
+        <v>1836</v>
+      </c>
+    </row>
+    <row r="611" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A611" s="1">
+        <v>9729839883</v>
+      </c>
+      <c r="B611" s="2" t="s">
+        <v>1855</v>
+      </c>
+      <c r="C611" s="2" t="s">
+        <v>1819</v>
+      </c>
+      <c r="D611" t="s">
+        <v>1837</v>
+      </c>
+    </row>
+    <row r="612" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A612" s="1">
+        <v>12208649869</v>
+      </c>
+      <c r="B612" s="2" t="s">
+        <v>1856</v>
+      </c>
+      <c r="C612" s="2" t="s">
+        <v>1820</v>
+      </c>
+      <c r="D612" t="s">
+        <v>1838</v>
+      </c>
+    </row>
+    <row r="613" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A613" s="1">
+        <v>5099807402</v>
+      </c>
+      <c r="B613" s="2" t="s">
+        <v>1857</v>
+      </c>
+      <c r="C613" s="2" t="s">
+        <v>1821</v>
+      </c>
+      <c r="D613" t="s">
+        <v>1839</v>
+      </c>
+    </row>
+    <row r="614" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A614" s="1">
+        <v>20991362896</v>
+      </c>
+      <c r="B614" s="2" t="s">
+        <v>1858</v>
+      </c>
+      <c r="C614" s="2" t="s">
+        <v>1822</v>
+      </c>
+      <c r="D614" t="s">
+        <v>1840</v>
+      </c>
+    </row>
+    <row r="615" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A615" s="1">
+        <v>46762698468</v>
+      </c>
+      <c r="B615" s="2" t="s">
+        <v>1859</v>
+      </c>
+      <c r="C615" s="2" t="s">
+        <v>1823</v>
+      </c>
+      <c r="D615" t="s">
+        <v>1841</v>
+      </c>
+    </row>
+    <row r="616" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A616" s="1">
+        <v>28811532833</v>
+      </c>
+      <c r="B616" s="2" t="s">
+        <v>1860</v>
+      </c>
+      <c r="C616" s="2" t="s">
+        <v>1824</v>
+      </c>
+      <c r="D616" t="s">
+        <v>1842</v>
+      </c>
+    </row>
+    <row r="617" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A617" s="1">
+        <v>37980635833</v>
+      </c>
+      <c r="B617" s="2" t="s">
+        <v>1861</v>
+      </c>
+      <c r="C617" s="2" t="s">
+        <v>1825</v>
+      </c>
+      <c r="D617" t="s">
+        <v>1843</v>
+      </c>
+    </row>
+    <row r="618" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A618" s="1">
+        <v>36697913886</v>
+      </c>
+      <c r="B618" s="2" t="s">
+        <v>1862</v>
+      </c>
+      <c r="C618" s="2" t="s">
+        <v>1826</v>
+      </c>
+      <c r="D618" t="s">
+        <v>1844</v>
+      </c>
+    </row>
+    <row r="619" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A619" s="1">
+        <v>9865807831</v>
+      </c>
+      <c r="B619" s="2" t="s">
+        <v>1863</v>
+      </c>
+      <c r="C619" s="2" t="s">
+        <v>1827</v>
+      </c>
+      <c r="D619" t="s">
+        <v>1845</v>
+      </c>
+    </row>
+    <row r="620" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A620" s="1">
+        <v>26644532896</v>
+      </c>
+      <c r="B620" s="2" t="s">
+        <v>1864</v>
+      </c>
+      <c r="C620" s="2" t="s">
+        <v>1828</v>
+      </c>
+      <c r="D620" t="s">
+        <v>1846</v>
+      </c>
+    </row>
+    <row r="621" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A621" s="1">
+        <v>14474783808</v>
+      </c>
+      <c r="B621" s="2" t="s">
+        <v>1865</v>
+      </c>
+      <c r="C621" s="2" t="s">
+        <v>1829</v>
+      </c>
+      <c r="D621" t="s">
+        <v>1847</v>
+      </c>
+    </row>
+    <row r="622" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A622" s="1">
+        <v>23170509845</v>
+      </c>
+      <c r="B622" s="2" t="s">
+        <v>1866</v>
+      </c>
+      <c r="C622" s="2" t="s">
+        <v>1830</v>
+      </c>
+      <c r="D622" t="s">
+        <v>1848</v>
+      </c>
+    </row>
   </sheetData>
   <autoFilter ref="A1:D604"/>
   <pageMargins left="0.511811024" right="0.511811024" top="0.78740157499999996" bottom="0.78740157499999996" header="0.31496062000000002" footer="0.31496062000000002"/>

--- a/dados.xlsx
+++ b/dados.xlsx
@@ -15,7 +15,7 @@
     <sheet name="data" sheetId="1" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">data!$A$1:$D$604</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">data!$A$1:$D$622</definedName>
   </definedNames>
   <calcPr calcId="152511"/>
   <extLst>
@@ -5646,12 +5646,18 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="2">
+  <fills count="3">
     <fill>
       <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFF00"/>
+        <bgColor indexed="64"/>
+      </patternFill>
     </fill>
   </fills>
   <borders count="1">
@@ -5666,10 +5672,11 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="3">
+  <cellXfs count="4">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -5950,6 +5957,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+  <sheetPr filterMode="1"/>
   <dimension ref="A1:D622"/>
   <sheetFormatPr defaultRowHeight="15.75" x14ac:dyDescent="0.25"/>
   <cols>
@@ -5974,7 +5982,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="2" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
       <c r="A2" s="1">
         <v>38404963819</v>
       </c>
@@ -5988,7 +5996,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="3" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
       <c r="A3" s="1">
         <v>18565029883</v>
       </c>
@@ -6002,7 +6010,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="4" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
       <c r="A4" s="1">
         <v>15012582810</v>
       </c>
@@ -6016,7 +6024,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="5" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
       <c r="A5" s="1">
         <v>8093509801</v>
       </c>
@@ -6030,7 +6038,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="6" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
       <c r="A6" s="1">
         <v>12207604802</v>
       </c>
@@ -6044,7 +6052,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="7" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
       <c r="A7" s="1">
         <v>30765135833</v>
       </c>
@@ -6058,7 +6066,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="8" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
       <c r="A8" s="1">
         <v>31943912831</v>
       </c>
@@ -6072,7 +6080,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="9" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
       <c r="A9" s="1">
         <v>25576439805</v>
       </c>
@@ -6086,7 +6094,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="10" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
       <c r="A10" s="1">
         <v>32535735830</v>
       </c>
@@ -6100,7 +6108,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="11" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
       <c r="A11" s="1">
         <v>14465896840</v>
       </c>
@@ -6114,7 +6122,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="12" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
       <c r="A12" s="1">
         <v>19915778856</v>
       </c>
@@ -6128,7 +6136,7 @@
         <v>36</v>
       </c>
     </row>
-    <row r="13" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
       <c r="A13" s="1">
         <v>24204890806</v>
       </c>
@@ -6142,7 +6150,7 @@
         <v>39</v>
       </c>
     </row>
-    <row r="14" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
       <c r="A14" s="1">
         <v>31282716824</v>
       </c>
@@ -6156,7 +6164,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="15" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
       <c r="A15" s="1">
         <v>23683129867</v>
       </c>
@@ -6170,7 +6178,7 @@
         <v>45</v>
       </c>
     </row>
-    <row r="16" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
       <c r="A16" s="1">
         <v>77690052487</v>
       </c>
@@ -6184,7 +6192,7 @@
         <v>48</v>
       </c>
     </row>
-    <row r="17" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
       <c r="A17" s="1">
         <v>35301393863</v>
       </c>
@@ -6198,7 +6206,7 @@
         <v>51</v>
       </c>
     </row>
-    <row r="18" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
       <c r="A18" s="1">
         <v>52549857801</v>
       </c>
@@ -6212,7 +6220,7 @@
         <v>54</v>
       </c>
     </row>
-    <row r="19" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
       <c r="A19" s="1">
         <v>40209619805</v>
       </c>
@@ -6226,7 +6234,7 @@
         <v>57</v>
       </c>
     </row>
-    <row r="20" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
       <c r="A20" s="1">
         <v>46494643825</v>
       </c>
@@ -6240,7 +6248,7 @@
         <v>60</v>
       </c>
     </row>
-    <row r="21" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
       <c r="A21" s="1">
         <v>19916435863</v>
       </c>
@@ -6254,7 +6262,7 @@
         <v>63</v>
       </c>
     </row>
-    <row r="22" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
       <c r="A22" s="1">
         <v>54311930828</v>
       </c>
@@ -6268,7 +6276,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="23" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
       <c r="A23" s="1">
         <v>47916071800</v>
       </c>
@@ -6282,7 +6290,7 @@
         <v>69</v>
       </c>
     </row>
-    <row r="24" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
       <c r="A24" s="1">
         <v>28044914803</v>
       </c>
@@ -6296,7 +6304,7 @@
         <v>72</v>
       </c>
     </row>
-    <row r="25" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
       <c r="A25" s="1">
         <v>24169816846</v>
       </c>
@@ -6310,7 +6318,7 @@
         <v>75</v>
       </c>
     </row>
-    <row r="26" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
       <c r="A26" s="1">
         <v>52796677818</v>
       </c>
@@ -6324,7 +6332,7 @@
         <v>78</v>
       </c>
     </row>
-    <row r="27" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
       <c r="A27" s="1">
         <v>24027156854</v>
       </c>
@@ -6338,7 +6346,7 @@
         <v>81</v>
       </c>
     </row>
-    <row r="28" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
       <c r="A28" s="1">
         <v>40453220860</v>
       </c>
@@ -6352,7 +6360,7 @@
         <v>84</v>
       </c>
     </row>
-    <row r="29" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
       <c r="A29" s="1">
         <v>53864401879</v>
       </c>
@@ -6366,7 +6374,7 @@
         <v>87</v>
       </c>
     </row>
-    <row r="30" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
       <c r="A30" s="1">
         <v>41642771813</v>
       </c>
@@ -6380,7 +6388,7 @@
         <v>90</v>
       </c>
     </row>
-    <row r="31" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
       <c r="A31" s="1">
         <v>53956561899</v>
       </c>
@@ -6394,7 +6402,7 @@
         <v>93</v>
       </c>
     </row>
-    <row r="32" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
       <c r="A32" s="1">
         <v>10334978866</v>
       </c>
@@ -6408,7 +6416,7 @@
         <v>96</v>
       </c>
     </row>
-    <row r="33" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="33" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
       <c r="A33" s="1">
         <v>12201427860</v>
       </c>
@@ -6422,7 +6430,7 @@
         <v>99</v>
       </c>
     </row>
-    <row r="34" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="34" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
       <c r="A34" s="1">
         <v>39553932835</v>
       </c>
@@ -6436,7 +6444,7 @@
         <v>102</v>
       </c>
     </row>
-    <row r="35" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="35" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
       <c r="A35" s="1">
         <v>40371382807</v>
       </c>
@@ -6450,7 +6458,7 @@
         <v>105</v>
       </c>
     </row>
-    <row r="36" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="36" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
       <c r="A36" s="1">
         <v>24027163800</v>
       </c>
@@ -6464,7 +6472,7 @@
         <v>108</v>
       </c>
     </row>
-    <row r="37" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="37" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
       <c r="A37" s="1">
         <v>86197410559</v>
       </c>
@@ -6478,7 +6486,7 @@
         <v>111</v>
       </c>
     </row>
-    <row r="38" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="38" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
       <c r="A38" s="1">
         <v>92924832853</v>
       </c>
@@ -6492,7 +6500,7 @@
         <v>114</v>
       </c>
     </row>
-    <row r="39" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="39" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
       <c r="A39" s="1">
         <v>27608561866</v>
       </c>
@@ -6506,7 +6514,7 @@
         <v>117</v>
       </c>
     </row>
-    <row r="40" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="40" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
       <c r="A40" s="1">
         <v>53370626896</v>
       </c>
@@ -6520,7 +6528,7 @@
         <v>120</v>
       </c>
     </row>
-    <row r="41" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="41" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
       <c r="A41" s="1">
         <v>13838573854</v>
       </c>
@@ -6534,7 +6542,7 @@
         <v>123</v>
       </c>
     </row>
-    <row r="42" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="42" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
       <c r="A42" s="1">
         <v>45921169846</v>
       </c>
@@ -6548,7 +6556,7 @@
         <v>126</v>
       </c>
     </row>
-    <row r="43" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="43" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
       <c r="A43" s="1">
         <v>23139885890</v>
       </c>
@@ -6562,7 +6570,7 @@
         <v>129</v>
       </c>
     </row>
-    <row r="44" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="44" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
       <c r="A44" s="1">
         <v>37389079800</v>
       </c>
@@ -6576,7 +6584,7 @@
         <v>132</v>
       </c>
     </row>
-    <row r="45" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="45" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
       <c r="A45" s="1">
         <v>34349878866</v>
       </c>
@@ -6590,7 +6598,7 @@
         <v>135</v>
       </c>
     </row>
-    <row r="46" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="46" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
       <c r="A46" s="1">
         <v>41428028870</v>
       </c>
@@ -6604,7 +6612,7 @@
         <v>138</v>
       </c>
     </row>
-    <row r="47" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="47" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
       <c r="A47" s="1">
         <v>10668577762</v>
       </c>
@@ -6618,7 +6626,7 @@
         <v>141</v>
       </c>
     </row>
-    <row r="48" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="48" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
       <c r="A48" s="1">
         <v>34543153871</v>
       </c>
@@ -6632,7 +6640,7 @@
         <v>144</v>
       </c>
     </row>
-    <row r="49" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="49" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
       <c r="A49" s="1">
         <v>31277915857</v>
       </c>
@@ -6646,7 +6654,7 @@
         <v>147</v>
       </c>
     </row>
-    <row r="50" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="50" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
       <c r="A50" s="1">
         <v>28494680889</v>
       </c>
@@ -6660,7 +6668,7 @@
         <v>150</v>
       </c>
     </row>
-    <row r="51" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="51" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
       <c r="A51" s="1">
         <v>6037483418</v>
       </c>
@@ -6674,7 +6682,7 @@
         <v>153</v>
       </c>
     </row>
-    <row r="52" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="52" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
       <c r="A52" s="1">
         <v>25753958877</v>
       </c>
@@ -6688,7 +6696,7 @@
         <v>156</v>
       </c>
     </row>
-    <row r="53" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="53" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
       <c r="A53" s="1">
         <v>9868535859</v>
       </c>
@@ -6702,7 +6710,7 @@
         <v>159</v>
       </c>
     </row>
-    <row r="54" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="54" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
       <c r="A54" s="1">
         <v>33015997882</v>
       </c>
@@ -6716,7 +6724,7 @@
         <v>162</v>
       </c>
     </row>
-    <row r="55" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="55" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
       <c r="A55" s="1">
         <v>12200049870</v>
       </c>
@@ -6730,7 +6738,7 @@
         <v>165</v>
       </c>
     </row>
-    <row r="56" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="56" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
       <c r="A56" s="1">
         <v>21491614862</v>
       </c>
@@ -6744,7 +6752,7 @@
         <v>168</v>
       </c>
     </row>
-    <row r="57" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="57" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
       <c r="A57" s="1">
         <v>29787401836</v>
       </c>
@@ -6758,7 +6766,7 @@
         <v>171</v>
       </c>
     </row>
-    <row r="58" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="58" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
       <c r="A58" s="1">
         <v>26187625846</v>
       </c>
@@ -6772,7 +6780,7 @@
         <v>174</v>
       </c>
     </row>
-    <row r="59" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="59" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
       <c r="A59" s="1">
         <v>32106419864</v>
       </c>
@@ -6786,7 +6794,7 @@
         <v>177</v>
       </c>
     </row>
-    <row r="60" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="60" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
       <c r="A60" s="1">
         <v>37808075809</v>
       </c>
@@ -6800,7 +6808,7 @@
         <v>180</v>
       </c>
     </row>
-    <row r="61" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="61" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
       <c r="A61" s="1">
         <v>35311653809</v>
       </c>
@@ -6814,7 +6822,7 @@
         <v>183</v>
       </c>
     </row>
-    <row r="62" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="62" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
       <c r="A62" s="1">
         <v>37831320881</v>
       </c>
@@ -6828,7 +6836,7 @@
         <v>186</v>
       </c>
     </row>
-    <row r="63" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="63" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
       <c r="A63" s="1">
         <v>40604264828</v>
       </c>
@@ -6842,7 +6850,7 @@
         <v>189</v>
       </c>
     </row>
-    <row r="64" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="64" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
       <c r="A64" s="1">
         <v>38928081807</v>
       </c>
@@ -6856,7 +6864,7 @@
         <v>192</v>
       </c>
     </row>
-    <row r="65" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="65" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
       <c r="A65" s="1">
         <v>40310402883</v>
       </c>
@@ -6870,7 +6878,7 @@
         <v>195</v>
       </c>
     </row>
-    <row r="66" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="66" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
       <c r="A66" s="1">
         <v>32335049852</v>
       </c>
@@ -6884,7 +6892,7 @@
         <v>198</v>
       </c>
     </row>
-    <row r="67" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="67" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
       <c r="A67" s="1">
         <v>27184046803</v>
       </c>
@@ -6898,7 +6906,7 @@
         <v>201</v>
       </c>
     </row>
-    <row r="68" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="68" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
       <c r="A68" s="1">
         <v>27110716856</v>
       </c>
@@ -6912,7 +6920,7 @@
         <v>204</v>
       </c>
     </row>
-    <row r="69" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="69" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
       <c r="A69" s="1">
         <v>33878717830</v>
       </c>
@@ -6926,7 +6934,7 @@
         <v>207</v>
       </c>
     </row>
-    <row r="70" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="70" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
       <c r="A70" s="1">
         <v>41060143860</v>
       </c>
@@ -6940,7 +6948,7 @@
         <v>210</v>
       </c>
     </row>
-    <row r="71" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="71" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
       <c r="A71" s="1">
         <v>1803068558</v>
       </c>
@@ -6954,7 +6962,7 @@
         <v>213</v>
       </c>
     </row>
-    <row r="72" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="72" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
       <c r="A72" s="1">
         <v>26825166883</v>
       </c>
@@ -6968,7 +6976,7 @@
         <v>216</v>
       </c>
     </row>
-    <row r="73" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="73" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
       <c r="A73" s="1">
         <v>16089702803</v>
       </c>
@@ -6982,7 +6990,7 @@
         <v>219</v>
       </c>
     </row>
-    <row r="74" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="74" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
       <c r="A74" s="1">
         <v>22307867848</v>
       </c>
@@ -6996,7 +7004,7 @@
         <v>222</v>
       </c>
     </row>
-    <row r="75" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="75" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
       <c r="A75" s="1">
         <v>12206503824</v>
       </c>
@@ -7010,7 +7018,7 @@
         <v>225</v>
       </c>
     </row>
-    <row r="76" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="76" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
       <c r="A76" s="1">
         <v>12207255875</v>
       </c>
@@ -7024,7 +7032,7 @@
         <v>228</v>
       </c>
     </row>
-    <row r="77" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="77" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
       <c r="A77" s="1">
         <v>4403227821</v>
       </c>
@@ -7038,7 +7046,7 @@
         <v>231</v>
       </c>
     </row>
-    <row r="78" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="78" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
       <c r="A78" s="1">
         <v>34951058839</v>
       </c>
@@ -7052,7 +7060,7 @@
         <v>234</v>
       </c>
     </row>
-    <row r="79" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="79" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
       <c r="A79" s="1">
         <v>23946451802</v>
       </c>
@@ -7066,7 +7074,7 @@
         <v>237</v>
       </c>
     </row>
-    <row r="80" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="80" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
       <c r="A80" s="1">
         <v>3340408840</v>
       </c>
@@ -7080,7 +7088,7 @@
         <v>240</v>
       </c>
     </row>
-    <row r="81" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="81" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
       <c r="A81" s="1">
         <v>24102581820</v>
       </c>
@@ -7094,7 +7102,7 @@
         <v>243</v>
       </c>
     </row>
-    <row r="82" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="82" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
       <c r="A82" s="1">
         <v>53047882819</v>
       </c>
@@ -7108,7 +7116,7 @@
         <v>246</v>
       </c>
     </row>
-    <row r="83" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="83" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
       <c r="A83" s="1">
         <v>42928959882</v>
       </c>
@@ -7122,7 +7130,7 @@
         <v>249</v>
       </c>
     </row>
-    <row r="84" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="84" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
       <c r="A84" s="1">
         <v>54300414831</v>
       </c>
@@ -7136,7 +7144,7 @@
         <v>252</v>
       </c>
     </row>
-    <row r="85" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="85" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
       <c r="A85" s="1">
         <v>14469946869</v>
       </c>
@@ -7150,7 +7158,7 @@
         <v>255</v>
       </c>
     </row>
-    <row r="86" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="86" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
       <c r="A86" s="1">
         <v>12209844851</v>
       </c>
@@ -7164,7 +7172,7 @@
         <v>258</v>
       </c>
     </row>
-    <row r="87" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="87" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
       <c r="A87" s="1">
         <v>59426496858</v>
       </c>
@@ -7178,7 +7186,7 @@
         <v>261</v>
       </c>
     </row>
-    <row r="88" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="88" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
       <c r="A88" s="1">
         <v>36820697805</v>
       </c>
@@ -7192,7 +7200,7 @@
         <v>264</v>
       </c>
     </row>
-    <row r="89" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="89" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
       <c r="A89" s="1">
         <v>44968090870</v>
       </c>
@@ -7206,7 +7214,7 @@
         <v>267</v>
       </c>
     </row>
-    <row r="90" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="90" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
       <c r="A90" s="1">
         <v>43637093839</v>
       </c>
@@ -7220,7 +7228,7 @@
         <v>270</v>
       </c>
     </row>
-    <row r="91" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="91" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
       <c r="A91" s="1">
         <v>44793150802</v>
       </c>
@@ -7234,7 +7242,7 @@
         <v>273</v>
       </c>
     </row>
-    <row r="92" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="92" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
       <c r="A92" s="1">
         <v>99384400297</v>
       </c>
@@ -7248,7 +7256,7 @@
         <v>276</v>
       </c>
     </row>
-    <row r="93" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="93" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
       <c r="A93" s="1">
         <v>39686692827</v>
       </c>
@@ -7262,7 +7270,7 @@
         <v>279</v>
       </c>
     </row>
-    <row r="94" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="94" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
       <c r="A94" s="1">
         <v>35856575830</v>
       </c>
@@ -7276,7 +7284,7 @@
         <v>282</v>
       </c>
     </row>
-    <row r="95" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="95" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
       <c r="A95" s="1">
         <v>45520256861</v>
       </c>
@@ -7290,7 +7298,7 @@
         <v>285</v>
       </c>
     </row>
-    <row r="96" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="96" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
       <c r="A96" s="1">
         <v>21945744847</v>
       </c>
@@ -7304,7 +7312,7 @@
         <v>288</v>
       </c>
     </row>
-    <row r="97" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="97" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
       <c r="A97" s="1">
         <v>36423348812</v>
       </c>
@@ -7318,7 +7326,7 @@
         <v>291</v>
       </c>
     </row>
-    <row r="98" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="98" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
       <c r="A98" s="1">
         <v>20990793826</v>
       </c>
@@ -7332,7 +7340,7 @@
         <v>294</v>
       </c>
     </row>
-    <row r="99" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="99" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
       <c r="A99" s="1">
         <v>41577861817</v>
       </c>
@@ -7346,7 +7354,7 @@
         <v>297</v>
       </c>
     </row>
-    <row r="100" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="100" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
       <c r="A100" s="1">
         <v>9868110840</v>
       </c>
@@ -7360,7 +7368,7 @@
         <v>300</v>
       </c>
     </row>
-    <row r="101" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="101" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
       <c r="A101" s="1">
         <v>33292585864</v>
       </c>
@@ -7374,7 +7382,7 @@
         <v>303</v>
       </c>
     </row>
-    <row r="102" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="102" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
       <c r="A102" s="1">
         <v>34814331827</v>
       </c>
@@ -7388,7 +7396,7 @@
         <v>306</v>
       </c>
     </row>
-    <row r="103" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="103" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
       <c r="A103" s="1">
         <v>36960937850</v>
       </c>
@@ -7402,7 +7410,7 @@
         <v>309</v>
       </c>
     </row>
-    <row r="104" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="104" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
       <c r="A104" s="1">
         <v>39063654847</v>
       </c>
@@ -7416,7 +7424,7 @@
         <v>312</v>
       </c>
     </row>
-    <row r="105" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="105" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
       <c r="A105" s="1">
         <v>35606129850</v>
       </c>
@@ -7430,7 +7438,7 @@
         <v>315</v>
       </c>
     </row>
-    <row r="106" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="106" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
       <c r="A106" s="1">
         <v>1410037827</v>
       </c>
@@ -7444,7 +7452,7 @@
         <v>318</v>
       </c>
     </row>
-    <row r="107" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="107" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
       <c r="A107" s="1">
         <v>12198073897</v>
       </c>
@@ -7458,7 +7466,7 @@
         <v>321</v>
       </c>
     </row>
-    <row r="108" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="108" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
       <c r="A108" s="1">
         <v>26534446820</v>
       </c>
@@ -7472,7 +7480,7 @@
         <v>324</v>
       </c>
     </row>
-    <row r="109" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="109" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
       <c r="A109" s="1">
         <v>13838479831</v>
       </c>
@@ -7486,7 +7494,7 @@
         <v>327</v>
       </c>
     </row>
-    <row r="110" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="110" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
       <c r="A110" s="1">
         <v>18568500803</v>
       </c>
@@ -7500,7 +7508,7 @@
         <v>330</v>
       </c>
     </row>
-    <row r="111" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="111" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
       <c r="A111" s="1">
         <v>8115349879</v>
       </c>
@@ -7514,7 +7522,7 @@
         <v>333</v>
       </c>
     </row>
-    <row r="112" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="112" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
       <c r="A112" s="1">
         <v>13279621879</v>
       </c>
@@ -7528,7 +7536,7 @@
         <v>336</v>
       </c>
     </row>
-    <row r="113" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="113" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
       <c r="A113" s="1">
         <v>12193323801</v>
       </c>
@@ -7542,7 +7550,7 @@
         <v>339</v>
       </c>
     </row>
-    <row r="114" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="114" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
       <c r="A114" s="1">
         <v>63412551791</v>
       </c>
@@ -7556,7 +7564,7 @@
         <v>342</v>
       </c>
     </row>
-    <row r="115" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="115" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
       <c r="A115" s="1">
         <v>32098986858</v>
       </c>
@@ -7570,7 +7578,7 @@
         <v>345</v>
       </c>
     </row>
-    <row r="116" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="116" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
       <c r="A116" s="1">
         <v>37672038800</v>
       </c>
@@ -7584,7 +7592,7 @@
         <v>348</v>
       </c>
     </row>
-    <row r="117" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="117" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
       <c r="A117" s="1">
         <v>3004205874</v>
       </c>
@@ -7598,7 +7606,7 @@
         <v>351</v>
       </c>
     </row>
-    <row r="118" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="118" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
       <c r="A118" s="1">
         <v>19908871803</v>
       </c>
@@ -7612,7 +7620,7 @@
         <v>354</v>
       </c>
     </row>
-    <row r="119" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="119" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
       <c r="A119" s="1">
         <v>9347616710</v>
       </c>
@@ -7626,7 +7634,7 @@
         <v>357</v>
       </c>
     </row>
-    <row r="120" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="120" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
       <c r="A120" s="1">
         <v>39781066806</v>
       </c>
@@ -7640,7 +7648,7 @@
         <v>360</v>
       </c>
     </row>
-    <row r="121" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="121" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
       <c r="A121" s="1">
         <v>25510896892</v>
       </c>
@@ -7654,7 +7662,7 @@
         <v>363</v>
       </c>
     </row>
-    <row r="122" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="122" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
       <c r="A122" s="1">
         <v>9291193801</v>
       </c>
@@ -7668,7 +7676,7 @@
         <v>366</v>
       </c>
     </row>
-    <row r="123" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="123" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
       <c r="A123" s="1">
         <v>46066485890</v>
       </c>
@@ -7682,7 +7690,7 @@
         <v>369</v>
       </c>
     </row>
-    <row r="124" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="124" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
       <c r="A124" s="1">
         <v>31895482852</v>
       </c>
@@ -7696,7 +7704,7 @@
         <v>372</v>
       </c>
     </row>
-    <row r="125" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="125" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
       <c r="A125" s="1">
         <v>47382853861</v>
       </c>
@@ -7710,7 +7718,7 @@
         <v>375</v>
       </c>
     </row>
-    <row r="126" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="126" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
       <c r="A126" s="1">
         <v>35607453812</v>
       </c>
@@ -7724,7 +7732,7 @@
         <v>378</v>
       </c>
     </row>
-    <row r="127" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="127" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
       <c r="A127" s="1">
         <v>33468262876</v>
       </c>
@@ -7738,7 +7746,7 @@
         <v>381</v>
       </c>
     </row>
-    <row r="128" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="128" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
       <c r="A128" s="1">
         <v>43101036852</v>
       </c>
@@ -7752,7 +7760,7 @@
         <v>384</v>
       </c>
     </row>
-    <row r="129" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="129" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
       <c r="A129" s="1">
         <v>37848774864</v>
       </c>
@@ -7766,7 +7774,7 @@
         <v>387</v>
       </c>
     </row>
-    <row r="130" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="130" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
       <c r="A130" s="1">
         <v>36413409851</v>
       </c>
@@ -7780,7 +7788,7 @@
         <v>390</v>
       </c>
     </row>
-    <row r="131" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="131" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
       <c r="A131" s="1">
         <v>35312518808</v>
       </c>
@@ -7794,7 +7802,7 @@
         <v>393</v>
       </c>
     </row>
-    <row r="132" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="132" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
       <c r="A132" s="1">
         <v>23147077888</v>
       </c>
@@ -7808,7 +7816,7 @@
         <v>396</v>
       </c>
     </row>
-    <row r="133" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="133" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
       <c r="A133" s="1">
         <v>22923717821</v>
       </c>
@@ -7822,7 +7830,7 @@
         <v>399</v>
       </c>
     </row>
-    <row r="134" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="134" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
       <c r="A134" s="1">
         <v>13247305874</v>
       </c>
@@ -7836,7 +7844,7 @@
         <v>402</v>
       </c>
     </row>
-    <row r="135" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="135" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
       <c r="A135" s="1">
         <v>13839299802</v>
       </c>
@@ -7850,7 +7858,7 @@
         <v>405</v>
       </c>
     </row>
-    <row r="136" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="136" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
       <c r="A136" s="1">
         <v>7249387880</v>
       </c>
@@ -7864,7 +7872,7 @@
         <v>408</v>
       </c>
     </row>
-    <row r="137" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="137" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
       <c r="A137" s="1">
         <v>28101340300</v>
       </c>
@@ -7878,7 +7886,7 @@
         <v>411</v>
       </c>
     </row>
-    <row r="138" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="138" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
       <c r="A138" s="1">
         <v>43556035391</v>
       </c>
@@ -7892,7 +7900,7 @@
         <v>414</v>
       </c>
     </row>
-    <row r="139" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="139" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
       <c r="A139" s="1">
         <v>32178793843</v>
       </c>
@@ -7906,7 +7914,7 @@
         <v>417</v>
       </c>
     </row>
-    <row r="140" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="140" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
       <c r="A140" s="1">
         <v>69383499672</v>
       </c>
@@ -7920,7 +7928,7 @@
         <v>420</v>
       </c>
     </row>
-    <row r="141" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="141" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
       <c r="A141" s="1">
         <v>37889345810</v>
       </c>
@@ -7934,7 +7942,7 @@
         <v>423</v>
       </c>
     </row>
-    <row r="142" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="142" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
       <c r="A142" s="1">
         <v>31625519869</v>
       </c>
@@ -7948,7 +7956,7 @@
         <v>426</v>
       </c>
     </row>
-    <row r="143" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="143" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
       <c r="A143" s="1">
         <v>10972813888</v>
       </c>
@@ -7962,7 +7970,7 @@
         <v>429</v>
       </c>
     </row>
-    <row r="144" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="144" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
       <c r="A144" s="1">
         <v>10969740883</v>
       </c>
@@ -7976,7 +7984,7 @@
         <v>432</v>
       </c>
     </row>
-    <row r="145" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="145" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
       <c r="A145" s="1">
         <v>10583767800</v>
       </c>
@@ -7990,7 +7998,7 @@
         <v>435</v>
       </c>
     </row>
-    <row r="146" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="146" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
       <c r="A146" s="1">
         <v>12193564841</v>
       </c>
@@ -8004,7 +8012,7 @@
         <v>438</v>
       </c>
     </row>
-    <row r="147" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="147" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
       <c r="A147" s="1">
         <v>47398691874</v>
       </c>
@@ -8018,7 +8026,7 @@
         <v>441</v>
       </c>
     </row>
-    <row r="148" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="148" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
       <c r="A148" s="1">
         <v>33352508852</v>
       </c>
@@ -8032,7 +8040,7 @@
         <v>444</v>
       </c>
     </row>
-    <row r="149" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="149" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
       <c r="A149" s="1">
         <v>31237783801</v>
       </c>
@@ -8046,7 +8054,7 @@
         <v>447</v>
       </c>
     </row>
-    <row r="150" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="150" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
       <c r="A150" s="1">
         <v>1119067685</v>
       </c>
@@ -8060,7 +8068,7 @@
         <v>450</v>
       </c>
     </row>
-    <row r="151" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="151" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
       <c r="A151" s="1">
         <v>7239579832</v>
       </c>
@@ -8074,7 +8082,7 @@
         <v>453</v>
       </c>
     </row>
-    <row r="152" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="152" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
       <c r="A152" s="1">
         <v>19913548861</v>
       </c>
@@ -8088,7 +8096,7 @@
         <v>456</v>
       </c>
     </row>
-    <row r="153" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="153" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
       <c r="A153" s="1">
         <v>14476293883</v>
       </c>
@@ -8102,7 +8110,7 @@
         <v>459</v>
       </c>
     </row>
-    <row r="154" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="154" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
       <c r="A154" s="1">
         <v>35696274897</v>
       </c>
@@ -8116,7 +8124,7 @@
         <v>462</v>
       </c>
     </row>
-    <row r="155" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="155" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
       <c r="A155" s="1">
         <v>9309226897</v>
       </c>
@@ -8130,7 +8138,7 @@
         <v>465</v>
       </c>
     </row>
-    <row r="156" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="156" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
       <c r="A156" s="1">
         <v>36011918816</v>
       </c>
@@ -8144,7 +8152,7 @@
         <v>468</v>
       </c>
     </row>
-    <row r="157" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="157" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
       <c r="A157" s="1">
         <v>10971207836</v>
       </c>
@@ -8158,7 +8166,7 @@
         <v>471</v>
       </c>
     </row>
-    <row r="158" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="158" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
       <c r="A158" s="1">
         <v>15016966885</v>
       </c>
@@ -8172,7 +8180,7 @@
         <v>474</v>
       </c>
     </row>
-    <row r="159" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="159" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
       <c r="A159" s="1">
         <v>35910929836</v>
       </c>
@@ -8186,7 +8194,7 @@
         <v>477</v>
       </c>
     </row>
-    <row r="160" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="160" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
       <c r="A160" s="1">
         <v>37838009863</v>
       </c>
@@ -8200,7 +8208,7 @@
         <v>480</v>
       </c>
     </row>
-    <row r="161" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="161" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
       <c r="A161" s="1">
         <v>12211439802</v>
       </c>
@@ -8214,7 +8222,7 @@
         <v>483</v>
       </c>
     </row>
-    <row r="162" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="162" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
       <c r="A162" s="1">
         <v>26745170850</v>
       </c>
@@ -8228,7 +8236,7 @@
         <v>486</v>
       </c>
     </row>
-    <row r="163" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="163" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
       <c r="A163" s="1">
         <v>40422223824</v>
       </c>
@@ -8242,7 +8250,7 @@
         <v>489</v>
       </c>
     </row>
-    <row r="164" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="164" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
       <c r="A164" s="1">
         <v>19919609803</v>
       </c>
@@ -8256,7 +8264,7 @@
         <v>492</v>
       </c>
     </row>
-    <row r="165" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="165" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
       <c r="A165" s="1">
         <v>28028643</v>
       </c>
@@ -8270,7 +8278,7 @@
         <v>495</v>
       </c>
     </row>
-    <row r="166" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="166" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
       <c r="A166" s="1">
         <v>53639178823</v>
       </c>
@@ -8284,7 +8292,7 @@
         <v>498</v>
       </c>
     </row>
-    <row r="167" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="167" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
       <c r="A167" s="1">
         <v>37755998860</v>
       </c>
@@ -8298,7 +8306,7 @@
         <v>501</v>
       </c>
     </row>
-    <row r="168" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="168" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
       <c r="A168" s="1">
         <v>26649895881</v>
       </c>
@@ -8312,7 +8320,7 @@
         <v>504</v>
       </c>
     </row>
-    <row r="169" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="169" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
       <c r="A169" s="1">
         <v>36182961856</v>
       </c>
@@ -8326,7 +8334,7 @@
         <v>507</v>
       </c>
     </row>
-    <row r="170" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="170" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
       <c r="A170" s="1">
         <v>33840017882</v>
       </c>
@@ -8340,7 +8348,7 @@
         <v>510</v>
       </c>
     </row>
-    <row r="171" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="171" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
       <c r="A171" s="1">
         <v>24035059862</v>
       </c>
@@ -8354,7 +8362,7 @@
         <v>513</v>
       </c>
     </row>
-    <row r="172" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="172" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
       <c r="A172" s="1">
         <v>10982968850</v>
       </c>
@@ -8368,7 +8376,7 @@
         <v>516</v>
       </c>
     </row>
-    <row r="173" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="173" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
       <c r="A173" s="1">
         <v>36832417802</v>
       </c>
@@ -8382,7 +8390,7 @@
         <v>519</v>
       </c>
     </row>
-    <row r="174" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="174" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
       <c r="A174" s="1">
         <v>32233315812</v>
       </c>
@@ -8396,7 +8404,7 @@
         <v>522</v>
       </c>
     </row>
-    <row r="175" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="175" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
       <c r="A175" s="1">
         <v>31497220807</v>
       </c>
@@ -8410,7 +8418,7 @@
         <v>525</v>
       </c>
     </row>
-    <row r="176" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="176" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
       <c r="A176" s="1">
         <v>49057621894</v>
       </c>
@@ -8424,7 +8432,7 @@
         <v>528</v>
       </c>
     </row>
-    <row r="177" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="177" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
       <c r="A177" s="1">
         <v>30534120806</v>
       </c>
@@ -8438,7 +8446,7 @@
         <v>531</v>
       </c>
     </row>
-    <row r="178" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="178" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
       <c r="A178" s="1">
         <v>3042836495</v>
       </c>
@@ -8452,7 +8460,7 @@
         <v>534</v>
       </c>
     </row>
-    <row r="179" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="179" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
       <c r="A179" s="1">
         <v>18195176755</v>
       </c>
@@ -8466,7 +8474,7 @@
         <v>537</v>
       </c>
     </row>
-    <row r="180" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="180" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
       <c r="A180" s="1">
         <v>22243513803</v>
       </c>
@@ -8480,7 +8488,7 @@
         <v>540</v>
       </c>
     </row>
-    <row r="181" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="181" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
       <c r="A181" s="1">
         <v>45250838839</v>
       </c>
@@ -8494,7 +8502,7 @@
         <v>543</v>
       </c>
     </row>
-    <row r="182" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="182" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
       <c r="A182" s="1">
         <v>12199261832</v>
       </c>
@@ -8508,7 +8516,7 @@
         <v>546</v>
       </c>
     </row>
-    <row r="183" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="183" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
       <c r="A183" s="1">
         <v>28352461850</v>
       </c>
@@ -8522,7 +8530,7 @@
         <v>549</v>
       </c>
     </row>
-    <row r="184" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="184" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
       <c r="A184" s="1">
         <v>24760354832</v>
       </c>
@@ -8536,7 +8544,7 @@
         <v>552</v>
       </c>
     </row>
-    <row r="185" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="185" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
       <c r="A185" s="1">
         <v>43885983800</v>
       </c>
@@ -8550,7 +8558,7 @@
         <v>555</v>
       </c>
     </row>
-    <row r="186" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="186" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
       <c r="A186" s="1">
         <v>49765432852</v>
       </c>
@@ -8564,7 +8572,7 @@
         <v>558</v>
       </c>
     </row>
-    <row r="187" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="187" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
       <c r="A187" s="1">
         <v>41428029842</v>
       </c>
@@ -8578,7 +8586,7 @@
         <v>561</v>
       </c>
     </row>
-    <row r="188" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="188" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
       <c r="A188" s="1">
         <v>31851283897</v>
       </c>
@@ -8592,7 +8600,7 @@
         <v>564</v>
       </c>
     </row>
-    <row r="189" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="189" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
       <c r="A189" s="1">
         <v>41637974833</v>
       </c>
@@ -8606,7 +8614,7 @@
         <v>567</v>
       </c>
     </row>
-    <row r="190" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="190" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
       <c r="A190" s="1">
         <v>9866344843</v>
       </c>
@@ -8620,7 +8628,7 @@
         <v>570</v>
       </c>
     </row>
-    <row r="191" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="191" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
       <c r="A191" s="1">
         <v>92926860897</v>
       </c>
@@ -8634,7 +8642,7 @@
         <v>573</v>
       </c>
     </row>
-    <row r="192" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="192" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
       <c r="A192" s="1">
         <v>33954654890</v>
       </c>
@@ -8648,7 +8656,7 @@
         <v>576</v>
       </c>
     </row>
-    <row r="193" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="193" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
       <c r="A193" s="1">
         <v>3902139854</v>
       </c>
@@ -8662,7 +8670,7 @@
         <v>579</v>
       </c>
     </row>
-    <row r="194" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="194" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
       <c r="A194" s="1">
         <v>38012949865</v>
       </c>
@@ -8676,7 +8684,7 @@
         <v>582</v>
       </c>
     </row>
-    <row r="195" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="195" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
       <c r="A195" s="1">
         <v>46472015899</v>
       </c>
@@ -8690,7 +8698,7 @@
         <v>585</v>
       </c>
     </row>
-    <row r="196" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="196" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
       <c r="A196" s="1">
         <v>57416937841</v>
       </c>
@@ -8704,7 +8712,7 @@
         <v>588</v>
       </c>
     </row>
-    <row r="197" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="197" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
       <c r="A197" s="1">
         <v>53075173860</v>
       </c>
@@ -8718,7 +8726,7 @@
         <v>591</v>
       </c>
     </row>
-    <row r="198" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="198" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
       <c r="A198" s="1">
         <v>36494700802</v>
       </c>
@@ -8732,7 +8740,7 @@
         <v>594</v>
       </c>
     </row>
-    <row r="199" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="199" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
       <c r="A199" s="1">
         <v>27889166800</v>
       </c>
@@ -8746,7 +8754,7 @@
         <v>597</v>
       </c>
     </row>
-    <row r="200" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="200" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
       <c r="A200" s="1">
         <v>42730508899</v>
       </c>
@@ -8760,7 +8768,7 @@
         <v>600</v>
       </c>
     </row>
-    <row r="201" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="201" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
       <c r="A201" s="1">
         <v>35297580862</v>
       </c>
@@ -8774,7 +8782,7 @@
         <v>603</v>
       </c>
     </row>
-    <row r="202" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="202" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
       <c r="A202" s="1">
         <v>32358919861</v>
       </c>
@@ -8788,7 +8796,7 @@
         <v>606</v>
       </c>
     </row>
-    <row r="203" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="203" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
       <c r="A203" s="1">
         <v>35415558829</v>
       </c>
@@ -8802,7 +8810,7 @@
         <v>609</v>
       </c>
     </row>
-    <row r="204" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="204" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
       <c r="A204" s="1">
         <v>36731840831</v>
       </c>
@@ -8816,7 +8824,7 @@
         <v>612</v>
       </c>
     </row>
-    <row r="205" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="205" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
       <c r="A205" s="1">
         <v>33405333857</v>
       </c>
@@ -8830,7 +8838,7 @@
         <v>615</v>
       </c>
     </row>
-    <row r="206" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="206" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
       <c r="A206" s="1">
         <v>90076143805</v>
       </c>
@@ -8844,7 +8852,7 @@
         <v>618</v>
       </c>
     </row>
-    <row r="207" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="207" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
       <c r="A207" s="1">
         <v>9868819881</v>
       </c>
@@ -8858,7 +8866,7 @@
         <v>621</v>
       </c>
     </row>
-    <row r="208" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="208" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
       <c r="A208" s="1">
         <v>30314343822</v>
       </c>
@@ -8872,7 +8880,7 @@
         <v>624</v>
       </c>
     </row>
-    <row r="209" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="209" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
       <c r="A209" s="1">
         <v>27188288895</v>
       </c>
@@ -8886,7 +8894,7 @@
         <v>627</v>
       </c>
     </row>
-    <row r="210" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="210" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
       <c r="A210" s="1">
         <v>36073783809</v>
       </c>
@@ -8900,7 +8908,7 @@
         <v>630</v>
       </c>
     </row>
-    <row r="211" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="211" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
       <c r="A211" s="1">
         <v>27842650802</v>
       </c>
@@ -8914,7 +8922,7 @@
         <v>633</v>
       </c>
     </row>
-    <row r="212" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="212" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
       <c r="A212" s="1">
         <v>45837347860</v>
       </c>
@@ -8928,7 +8936,7 @@
         <v>636</v>
       </c>
     </row>
-    <row r="213" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="213" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
       <c r="A213" s="1">
         <v>18384260869</v>
       </c>
@@ -8942,7 +8950,7 @@
         <v>639</v>
       </c>
     </row>
-    <row r="214" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="214" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
       <c r="A214" s="1">
         <v>35177309800</v>
       </c>
@@ -8956,7 +8964,7 @@
         <v>642</v>
       </c>
     </row>
-    <row r="215" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="215" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
       <c r="A215" s="1">
         <v>12194040803</v>
       </c>
@@ -8970,7 +8978,7 @@
         <v>645</v>
       </c>
     </row>
-    <row r="216" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="216" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
       <c r="A216" s="1">
         <v>10969815808</v>
       </c>
@@ -8984,7 +8992,7 @@
         <v>648</v>
       </c>
     </row>
-    <row r="217" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="217" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
       <c r="A217" s="1">
         <v>30009778802</v>
       </c>
@@ -8998,7 +9006,7 @@
         <v>651</v>
       </c>
     </row>
-    <row r="218" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="218" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
       <c r="A218" s="1">
         <v>7116858865</v>
       </c>
@@ -9012,7 +9020,7 @@
         <v>654</v>
       </c>
     </row>
-    <row r="219" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="219" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
       <c r="A219" s="1">
         <v>9871352875</v>
       </c>
@@ -9026,7 +9034,7 @@
         <v>657</v>
       </c>
     </row>
-    <row r="220" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="220" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
       <c r="A220" s="1">
         <v>2596280850</v>
       </c>
@@ -9040,7 +9048,7 @@
         <v>660</v>
       </c>
     </row>
-    <row r="221" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="221" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
       <c r="A221" s="1">
         <v>32897350873</v>
       </c>
@@ -9054,7 +9062,7 @@
         <v>663</v>
       </c>
     </row>
-    <row r="222" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="222" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
       <c r="A222" s="1">
         <v>27431914814</v>
       </c>
@@ -9068,7 +9076,7 @@
         <v>666</v>
       </c>
     </row>
-    <row r="223" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="223" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
       <c r="A223" s="1">
         <v>37534514878</v>
       </c>
@@ -9082,7 +9090,7 @@
         <v>669</v>
       </c>
     </row>
-    <row r="224" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="224" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
       <c r="A224" s="1">
         <v>48419421812</v>
       </c>
@@ -9096,7 +9104,7 @@
         <v>672</v>
       </c>
     </row>
-    <row r="225" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="225" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
       <c r="A225" s="1">
         <v>56841311825</v>
       </c>
@@ -9110,7 +9118,7 @@
         <v>675</v>
       </c>
     </row>
-    <row r="226" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="226" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
       <c r="A226" s="1">
         <v>54274580857</v>
       </c>
@@ -9124,7 +9132,7 @@
         <v>678</v>
       </c>
     </row>
-    <row r="227" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="227" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
       <c r="A227" s="1">
         <v>22312101858</v>
       </c>
@@ -9138,7 +9146,7 @@
         <v>681</v>
       </c>
     </row>
-    <row r="228" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="228" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
       <c r="A228" s="1">
         <v>16325809858</v>
       </c>
@@ -9152,7 +9160,7 @@
         <v>684</v>
       </c>
     </row>
-    <row r="229" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="229" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
       <c r="A229" s="1">
         <v>12191954804</v>
       </c>
@@ -9166,7 +9174,7 @@
         <v>687</v>
       </c>
     </row>
-    <row r="230" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="230" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
       <c r="A230" s="1">
         <v>7125770843</v>
       </c>
@@ -9180,7 +9188,7 @@
         <v>690</v>
       </c>
     </row>
-    <row r="231" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="231" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
       <c r="A231" s="1">
         <v>26412924833</v>
       </c>
@@ -9194,7 +9202,7 @@
         <v>693</v>
       </c>
     </row>
-    <row r="232" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="232" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
       <c r="A232" s="1">
         <v>21683466829</v>
       </c>
@@ -9208,7 +9216,7 @@
         <v>696</v>
       </c>
     </row>
-    <row r="233" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="233" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
       <c r="A233" s="1">
         <v>55094304860</v>
       </c>
@@ -9222,7 +9230,7 @@
         <v>699</v>
       </c>
     </row>
-    <row r="234" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="234" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
       <c r="A234" s="1">
         <v>12197200895</v>
       </c>
@@ -9236,7 +9244,7 @@
         <v>702</v>
       </c>
     </row>
-    <row r="235" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="235" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
       <c r="A235" s="1">
         <v>30284375896</v>
       </c>
@@ -9250,7 +9258,7 @@
         <v>705</v>
       </c>
     </row>
-    <row r="236" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="236" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
       <c r="A236" s="1">
         <v>27623967860</v>
       </c>
@@ -9264,7 +9272,7 @@
         <v>708</v>
       </c>
     </row>
-    <row r="237" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="237" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
       <c r="A237" s="1">
         <v>33369869829</v>
       </c>
@@ -9278,7 +9286,7 @@
         <v>711</v>
       </c>
     </row>
-    <row r="238" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="238" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
       <c r="A238" s="1">
         <v>41825965870</v>
       </c>
@@ -9292,7 +9300,7 @@
         <v>714</v>
       </c>
     </row>
-    <row r="239" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="239" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
       <c r="A239" s="1">
         <v>24698891892</v>
       </c>
@@ -9306,7 +9314,7 @@
         <v>717</v>
       </c>
     </row>
-    <row r="240" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="240" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
       <c r="A240" s="1">
         <v>23313567851</v>
       </c>
@@ -9320,7 +9328,7 @@
         <v>720</v>
       </c>
     </row>
-    <row r="241" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="241" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
       <c r="A241" s="1">
         <v>38617228873</v>
       </c>
@@ -9348,7 +9356,7 @@
         <v>726</v>
       </c>
     </row>
-    <row r="243" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="243" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
       <c r="A243" s="1">
         <v>12204504807</v>
       </c>
@@ -9362,7 +9370,7 @@
         <v>729</v>
       </c>
     </row>
-    <row r="244" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="244" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
       <c r="A244" s="1">
         <v>41527156850</v>
       </c>
@@ -9376,7 +9384,7 @@
         <v>732</v>
       </c>
     </row>
-    <row r="245" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="245" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
       <c r="A245" s="1">
         <v>42265499889</v>
       </c>
@@ -9390,7 +9398,7 @@
         <v>735</v>
       </c>
     </row>
-    <row r="246" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="246" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
       <c r="A246" s="1">
         <v>9051076673</v>
       </c>
@@ -9404,7 +9412,7 @@
         <v>738</v>
       </c>
     </row>
-    <row r="247" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="247" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
       <c r="A247" s="1">
         <v>34753256839</v>
       </c>
@@ -9418,7 +9426,7 @@
         <v>741</v>
       </c>
     </row>
-    <row r="248" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="248" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
       <c r="A248" s="1">
         <v>41352008858</v>
       </c>
@@ -9432,7 +9440,7 @@
         <v>744</v>
       </c>
     </row>
-    <row r="249" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="249" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
       <c r="A249" s="1">
         <v>26096186890</v>
       </c>
@@ -9446,7 +9454,7 @@
         <v>747</v>
       </c>
     </row>
-    <row r="250" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="250" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
       <c r="A250" s="1">
         <v>51098073886</v>
       </c>
@@ -9460,7 +9468,7 @@
         <v>750</v>
       </c>
     </row>
-    <row r="251" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="251" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
       <c r="A251" s="1">
         <v>46336267873</v>
       </c>
@@ -9474,7 +9482,7 @@
         <v>753</v>
       </c>
     </row>
-    <row r="252" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="252" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
       <c r="A252" s="1">
         <v>25420301890</v>
       </c>
@@ -9488,7 +9496,7 @@
         <v>756</v>
       </c>
     </row>
-    <row r="253" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="253" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
       <c r="A253" s="1">
         <v>9865978806</v>
       </c>
@@ -9502,7 +9510,7 @@
         <v>759</v>
       </c>
     </row>
-    <row r="254" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="254" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
       <c r="A254" s="1">
         <v>35609542820</v>
       </c>
@@ -9516,7 +9524,7 @@
         <v>762</v>
       </c>
     </row>
-    <row r="255" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="255" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
       <c r="A255" s="1">
         <v>7112570867</v>
       </c>
@@ -9530,7 +9538,7 @@
         <v>765</v>
       </c>
     </row>
-    <row r="256" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="256" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
       <c r="A256" s="1">
         <v>28524992824</v>
       </c>
@@ -9544,7 +9552,7 @@
         <v>768</v>
       </c>
     </row>
-    <row r="257" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="257" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
       <c r="A257" s="1">
         <v>39384936820</v>
       </c>
@@ -9558,7 +9566,7 @@
         <v>771</v>
       </c>
     </row>
-    <row r="258" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="258" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
       <c r="A258" s="1">
         <v>20993851819</v>
       </c>
@@ -9572,7 +9580,7 @@
         <v>774</v>
       </c>
     </row>
-    <row r="259" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="259" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
       <c r="A259" s="1">
         <v>15012973844</v>
       </c>
@@ -9586,7 +9594,7 @@
         <v>777</v>
       </c>
     </row>
-    <row r="260" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="260" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
       <c r="A260" s="1">
         <v>44495996835</v>
       </c>
@@ -9600,7 +9608,7 @@
         <v>780</v>
       </c>
     </row>
-    <row r="261" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="261" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
       <c r="A261" s="1">
         <v>1809018501</v>
       </c>
@@ -9614,7 +9622,7 @@
         <v>783</v>
       </c>
     </row>
-    <row r="262" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="262" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
       <c r="A262" s="1">
         <v>27075983806</v>
       </c>
@@ -9628,7 +9636,7 @@
         <v>786</v>
       </c>
     </row>
-    <row r="263" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="263" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
       <c r="A263" s="1">
         <v>3279881420</v>
       </c>
@@ -9642,7 +9650,7 @@
         <v>789</v>
       </c>
     </row>
-    <row r="264" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="264" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
       <c r="A264" s="1">
         <v>25963098823</v>
       </c>
@@ -9656,7 +9664,7 @@
         <v>792</v>
       </c>
     </row>
-    <row r="265" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="265" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
       <c r="A265" s="1">
         <v>39042842822</v>
       </c>
@@ -9670,7 +9678,7 @@
         <v>795</v>
       </c>
     </row>
-    <row r="266" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="266" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
       <c r="A266" s="1">
         <v>12921212897</v>
       </c>
@@ -9684,7 +9692,7 @@
         <v>798</v>
       </c>
     </row>
-    <row r="267" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="267" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
       <c r="A267" s="1">
         <v>23238172808</v>
       </c>
@@ -9698,7 +9706,7 @@
         <v>801</v>
       </c>
     </row>
-    <row r="268" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="268" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
       <c r="A268" s="1">
         <v>52910974855</v>
       </c>
@@ -9712,7 +9720,7 @@
         <v>804</v>
       </c>
     </row>
-    <row r="269" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="269" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
       <c r="A269" s="1">
         <v>18564685850</v>
       </c>
@@ -9726,7 +9734,7 @@
         <v>807</v>
       </c>
     </row>
-    <row r="270" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="270" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
       <c r="A270" s="1">
         <v>45954939837</v>
       </c>
@@ -9740,7 +9748,7 @@
         <v>810</v>
       </c>
     </row>
-    <row r="271" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="271" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
       <c r="A271" s="1">
         <v>56201669884</v>
       </c>
@@ -9754,7 +9762,7 @@
         <v>813</v>
       </c>
     </row>
-    <row r="272" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="272" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
       <c r="A272" s="1">
         <v>12198237830</v>
       </c>
@@ -9768,7 +9776,7 @@
         <v>816</v>
       </c>
     </row>
-    <row r="273" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="273" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
       <c r="A273" s="1">
         <v>39777858850</v>
       </c>
@@ -9782,7 +9790,7 @@
         <v>819</v>
       </c>
     </row>
-    <row r="274" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="274" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
       <c r="A274" s="1">
         <v>51297907825</v>
       </c>
@@ -9796,7 +9804,7 @@
         <v>822</v>
       </c>
     </row>
-    <row r="275" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="275" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
       <c r="A275" s="1">
         <v>38499283810</v>
       </c>
@@ -9810,7 +9818,7 @@
         <v>825</v>
       </c>
     </row>
-    <row r="276" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="276" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
       <c r="A276" s="1">
         <v>33237499870</v>
       </c>
@@ -9824,7 +9832,7 @@
         <v>828</v>
       </c>
     </row>
-    <row r="277" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="277" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
       <c r="A277" s="1">
         <v>13839338808</v>
       </c>
@@ -9838,7 +9846,7 @@
         <v>831</v>
       </c>
     </row>
-    <row r="278" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="278" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
       <c r="A278" s="1">
         <v>35635691854</v>
       </c>
@@ -9852,7 +9860,7 @@
         <v>834</v>
       </c>
     </row>
-    <row r="279" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="279" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
       <c r="A279" s="1">
         <v>24169217896</v>
       </c>
@@ -9866,7 +9874,7 @@
         <v>837</v>
       </c>
     </row>
-    <row r="280" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="280" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
       <c r="A280" s="1">
         <v>46129702841</v>
       </c>
@@ -9880,7 +9888,7 @@
         <v>840</v>
       </c>
     </row>
-    <row r="281" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="281" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
       <c r="A281" s="1">
         <v>26813957805</v>
       </c>
@@ -9894,7 +9902,7 @@
         <v>843</v>
       </c>
     </row>
-    <row r="282" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="282" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
       <c r="A282" s="1">
         <v>38688996857</v>
       </c>
@@ -9908,7 +9916,7 @@
         <v>846</v>
       </c>
     </row>
-    <row r="283" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="283" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
       <c r="A283" s="1">
         <v>8117689880</v>
       </c>
@@ -9922,7 +9930,7 @@
         <v>849</v>
       </c>
     </row>
-    <row r="284" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="284" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
       <c r="A284" s="1">
         <v>24184332854</v>
       </c>
@@ -9936,7 +9944,7 @@
         <v>852</v>
       </c>
     </row>
-    <row r="285" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="285" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
       <c r="A285" s="1">
         <v>59478208896</v>
       </c>
@@ -9950,7 +9958,7 @@
         <v>855</v>
       </c>
     </row>
-    <row r="286" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="286" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
       <c r="A286" s="1">
         <v>28201993802</v>
       </c>
@@ -9964,7 +9972,7 @@
         <v>858</v>
       </c>
     </row>
-    <row r="287" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="287" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
       <c r="A287" s="1">
         <v>10098150677</v>
       </c>
@@ -9978,7 +9986,7 @@
         <v>861</v>
       </c>
     </row>
-    <row r="288" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="288" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
       <c r="A288" s="1">
         <v>45945417807</v>
       </c>
@@ -9992,7 +10000,7 @@
         <v>864</v>
       </c>
     </row>
-    <row r="289" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="289" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
       <c r="A289" s="1">
         <v>34321901820</v>
       </c>
@@ -10006,7 +10014,7 @@
         <v>867</v>
       </c>
     </row>
-    <row r="290" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="290" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
       <c r="A290" s="1">
         <v>45624177810</v>
       </c>
@@ -10020,7 +10028,7 @@
         <v>870</v>
       </c>
     </row>
-    <row r="291" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="291" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
       <c r="A291" s="1">
         <v>24182914805</v>
       </c>
@@ -10034,7 +10042,7 @@
         <v>873</v>
       </c>
     </row>
-    <row r="292" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="292" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
       <c r="A292" s="1">
         <v>43072276897</v>
       </c>
@@ -10048,7 +10056,7 @@
         <v>876</v>
       </c>
     </row>
-    <row r="293" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="293" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
       <c r="A293" s="1">
         <v>43716804886</v>
       </c>
@@ -10062,7 +10070,7 @@
         <v>879</v>
       </c>
     </row>
-    <row r="294" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="294" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
       <c r="A294" s="1">
         <v>47960653852</v>
       </c>
@@ -10076,7 +10084,7 @@
         <v>882</v>
       </c>
     </row>
-    <row r="295" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="295" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
       <c r="A295" s="1">
         <v>38945761896</v>
       </c>
@@ -10090,7 +10098,7 @@
         <v>885</v>
       </c>
     </row>
-    <row r="296" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="296" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
       <c r="A296" s="1">
         <v>46257514894</v>
       </c>
@@ -10104,7 +10112,7 @@
         <v>888</v>
       </c>
     </row>
-    <row r="297" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="297" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
       <c r="A297" s="1">
         <v>12208083857</v>
       </c>
@@ -10118,7 +10126,7 @@
         <v>891</v>
       </c>
     </row>
-    <row r="298" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="298" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
       <c r="A298" s="1">
         <v>25649340803</v>
       </c>
@@ -10132,7 +10140,7 @@
         <v>894</v>
       </c>
     </row>
-    <row r="299" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="299" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
       <c r="A299" s="1">
         <v>35460670888</v>
       </c>
@@ -10146,7 +10154,7 @@
         <v>897</v>
       </c>
     </row>
-    <row r="300" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="300" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
       <c r="A300" s="1">
         <v>34298648877</v>
       </c>
@@ -10160,7 +10168,7 @@
         <v>900</v>
       </c>
     </row>
-    <row r="301" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="301" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
       <c r="A301" s="1">
         <v>97775550910</v>
       </c>
@@ -10174,7 +10182,7 @@
         <v>903</v>
       </c>
     </row>
-    <row r="302" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="302" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
       <c r="A302" s="1">
         <v>46937647875</v>
       </c>
@@ -10188,7 +10196,7 @@
         <v>906</v>
       </c>
     </row>
-    <row r="303" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="303" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
       <c r="A303" s="1">
         <v>9990043876</v>
       </c>
@@ -10202,7 +10210,7 @@
         <v>909</v>
       </c>
     </row>
-    <row r="304" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="304" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
       <c r="A304" s="1">
         <v>53646982896</v>
       </c>
@@ -10216,7 +10224,7 @@
         <v>912</v>
       </c>
     </row>
-    <row r="305" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="305" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
       <c r="A305" s="1">
         <v>51914139895</v>
       </c>
@@ -10230,7 +10238,7 @@
         <v>915</v>
       </c>
     </row>
-    <row r="306" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="306" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
       <c r="A306" s="1">
         <v>48107086830</v>
       </c>
@@ -10244,7 +10252,7 @@
         <v>918</v>
       </c>
     </row>
-    <row r="307" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="307" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
       <c r="A307" s="1">
         <v>46589867879</v>
       </c>
@@ -10258,7 +10266,7 @@
         <v>921</v>
       </c>
     </row>
-    <row r="308" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="308" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
       <c r="A308" s="1">
         <v>40035507810</v>
       </c>
@@ -10272,7 +10280,7 @@
         <v>924</v>
       </c>
     </row>
-    <row r="309" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="309" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
       <c r="A309" s="1">
         <v>43364046824</v>
       </c>
@@ -10286,7 +10294,7 @@
         <v>927</v>
       </c>
     </row>
-    <row r="310" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="310" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
       <c r="A310" s="1">
         <v>54470931802</v>
       </c>
@@ -10300,7 +10308,7 @@
         <v>930</v>
       </c>
     </row>
-    <row r="311" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="311" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
       <c r="A311" s="1">
         <v>33328246860</v>
       </c>
@@ -10314,7 +10322,7 @@
         <v>933</v>
       </c>
     </row>
-    <row r="312" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="312" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
       <c r="A312" s="1">
         <v>441052584</v>
       </c>
@@ -10328,7 +10336,7 @@
         <v>936</v>
       </c>
     </row>
-    <row r="313" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="313" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
       <c r="A313" s="1">
         <v>13839414830</v>
       </c>
@@ -10342,7 +10350,7 @@
         <v>939</v>
       </c>
     </row>
-    <row r="314" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="314" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
       <c r="A314" s="1">
         <v>31211776808</v>
       </c>
@@ -10356,7 +10364,7 @@
         <v>942</v>
       </c>
     </row>
-    <row r="315" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="315" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
       <c r="A315" s="1">
         <v>13832503838</v>
       </c>
@@ -10370,7 +10378,7 @@
         <v>945</v>
       </c>
     </row>
-    <row r="316" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="316" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
       <c r="A316" s="1">
         <v>4965530543</v>
       </c>
@@ -10384,7 +10392,7 @@
         <v>948</v>
       </c>
     </row>
-    <row r="317" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="317" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
       <c r="A317" s="1">
         <v>13838391829</v>
       </c>
@@ -10398,7 +10406,7 @@
         <v>951</v>
       </c>
     </row>
-    <row r="318" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="318" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
       <c r="A318" s="1">
         <v>22355118809</v>
       </c>
@@ -10412,7 +10420,7 @@
         <v>954</v>
       </c>
     </row>
-    <row r="319" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="319" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
       <c r="A319" s="1">
         <v>31904597890</v>
       </c>
@@ -10426,7 +10434,7 @@
         <v>957</v>
       </c>
     </row>
-    <row r="320" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="320" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
       <c r="A320" s="1">
         <v>9348205897</v>
       </c>
@@ -10440,7 +10448,7 @@
         <v>960</v>
       </c>
     </row>
-    <row r="321" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="321" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
       <c r="A321" s="1">
         <v>12204710890</v>
       </c>
@@ -10454,7 +10462,7 @@
         <v>963</v>
       </c>
     </row>
-    <row r="322" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="322" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
       <c r="A322" s="1">
         <v>39643485897</v>
       </c>
@@ -10468,7 +10476,7 @@
         <v>966</v>
       </c>
     </row>
-    <row r="323" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="323" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
       <c r="A323" s="1">
         <v>57729990873</v>
       </c>
@@ -10482,7 +10490,7 @@
         <v>969</v>
       </c>
     </row>
-    <row r="324" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="324" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
       <c r="A324" s="1">
         <v>42810095825</v>
       </c>
@@ -10496,7 +10504,7 @@
         <v>972</v>
       </c>
     </row>
-    <row r="325" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="325" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
       <c r="A325" s="1">
         <v>44383283810</v>
       </c>
@@ -10510,7 +10518,7 @@
         <v>975</v>
       </c>
     </row>
-    <row r="326" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="326" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
       <c r="A326" s="1">
         <v>8119882873</v>
       </c>
@@ -10524,7 +10532,7 @@
         <v>978</v>
       </c>
     </row>
-    <row r="327" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="327" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
       <c r="A327" s="1">
         <v>43313379877</v>
       </c>
@@ -10538,7 +10546,7 @@
         <v>981</v>
       </c>
     </row>
-    <row r="328" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="328" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
       <c r="A328" s="1">
         <v>22226769838</v>
       </c>
@@ -10552,7 +10560,7 @@
         <v>984</v>
       </c>
     </row>
-    <row r="329" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="329" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
       <c r="A329" s="1">
         <v>32553311885</v>
       </c>
@@ -10566,7 +10574,7 @@
         <v>987</v>
       </c>
     </row>
-    <row r="330" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="330" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
       <c r="A330" s="1">
         <v>40613714873</v>
       </c>
@@ -10580,7 +10588,7 @@
         <v>990</v>
       </c>
     </row>
-    <row r="331" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="331" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
       <c r="A331" s="1">
         <v>25773673843</v>
       </c>
@@ -10594,7 +10602,7 @@
         <v>993</v>
       </c>
     </row>
-    <row r="332" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="332" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
       <c r="A332" s="1">
         <v>2604743809</v>
       </c>
@@ -10608,7 +10616,7 @@
         <v>996</v>
       </c>
     </row>
-    <row r="333" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="333" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
       <c r="A333" s="1">
         <v>37227655873</v>
       </c>
@@ -10622,7 +10630,7 @@
         <v>999</v>
       </c>
     </row>
-    <row r="334" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="334" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
       <c r="A334" s="1">
         <v>45885967806</v>
       </c>
@@ -10636,7 +10644,7 @@
         <v>1002</v>
       </c>
     </row>
-    <row r="335" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="335" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
       <c r="A335" s="1">
         <v>28526402870</v>
       </c>
@@ -10650,7 +10658,7 @@
         <v>1005</v>
       </c>
     </row>
-    <row r="336" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="336" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
       <c r="A336" s="1">
         <v>12199357864</v>
       </c>
@@ -10664,7 +10672,7 @@
         <v>1008</v>
       </c>
     </row>
-    <row r="337" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="337" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
       <c r="A337" s="1">
         <v>16266352850</v>
       </c>
@@ -10678,7 +10686,7 @@
         <v>1011</v>
       </c>
     </row>
-    <row r="338" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="338" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
       <c r="A338" s="1">
         <v>39610231829</v>
       </c>
@@ -10692,7 +10700,7 @@
         <v>1014</v>
       </c>
     </row>
-    <row r="339" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="339" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
       <c r="A339" s="1">
         <v>12204968803</v>
       </c>
@@ -10706,7 +10714,7 @@
         <v>1017</v>
       </c>
     </row>
-    <row r="340" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="340" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
       <c r="A340" s="1">
         <v>567295370</v>
       </c>
@@ -10720,7 +10728,7 @@
         <v>1020</v>
       </c>
     </row>
-    <row r="341" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="341" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
       <c r="A341" s="1">
         <v>2601156813</v>
       </c>
@@ -10734,7 +10742,7 @@
         <v>1023</v>
       </c>
     </row>
-    <row r="342" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="342" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
       <c r="A342" s="1">
         <v>31318751861</v>
       </c>
@@ -10748,7 +10756,7 @@
         <v>1026</v>
       </c>
     </row>
-    <row r="343" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="343" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
       <c r="A343" s="1">
         <v>89977254753</v>
       </c>
@@ -10762,7 +10770,7 @@
         <v>1029</v>
       </c>
     </row>
-    <row r="344" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="344" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
       <c r="A344" s="1">
         <v>10972426841</v>
       </c>
@@ -10776,7 +10784,7 @@
         <v>1032</v>
       </c>
     </row>
-    <row r="345" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="345" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
       <c r="A345" s="1">
         <v>27159250850</v>
       </c>
@@ -10790,7 +10798,7 @@
         <v>1035</v>
       </c>
     </row>
-    <row r="346" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="346" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
       <c r="A346" s="1">
         <v>46336243850</v>
       </c>
@@ -10804,7 +10812,7 @@
         <v>1038</v>
       </c>
     </row>
-    <row r="347" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="347" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
       <c r="A347" s="1">
         <v>12191559859</v>
       </c>
@@ -10818,7 +10826,7 @@
         <v>1041</v>
       </c>
     </row>
-    <row r="348" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="348" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
       <c r="A348" s="1">
         <v>33925524886</v>
       </c>
@@ -10832,7 +10840,7 @@
         <v>1044</v>
       </c>
     </row>
-    <row r="349" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="349" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
       <c r="A349" s="1">
         <v>8121053897</v>
       </c>
@@ -10846,7 +10854,7 @@
         <v>1047</v>
       </c>
     </row>
-    <row r="350" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="350" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
       <c r="A350" s="1">
         <v>8119587871</v>
       </c>
@@ -10860,7 +10868,7 @@
         <v>1050</v>
       </c>
     </row>
-    <row r="351" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="351" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
       <c r="A351" s="1">
         <v>26482199860</v>
       </c>
@@ -10874,7 +10882,7 @@
         <v>1053</v>
       </c>
     </row>
-    <row r="352" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="352" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
       <c r="A352" s="1">
         <v>12199304825</v>
       </c>
@@ -10888,7 +10896,7 @@
         <v>1056</v>
       </c>
     </row>
-    <row r="353" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="353" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
       <c r="A353" s="1">
         <v>15968338822</v>
       </c>
@@ -10902,7 +10910,7 @@
         <v>1059</v>
       </c>
     </row>
-    <row r="354" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="354" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
       <c r="A354" s="1">
         <v>12210887852</v>
       </c>
@@ -10916,7 +10924,7 @@
         <v>1062</v>
       </c>
     </row>
-    <row r="355" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="355" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
       <c r="A355" s="1">
         <v>14460005832</v>
       </c>
@@ -10930,7 +10938,7 @@
         <v>1065</v>
       </c>
     </row>
-    <row r="356" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="356" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
       <c r="A356" s="1">
         <v>30122659880</v>
       </c>
@@ -10944,7 +10952,7 @@
         <v>1068</v>
       </c>
     </row>
-    <row r="357" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="357" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
       <c r="A357" s="1">
         <v>21518379800</v>
       </c>
@@ -10958,7 +10966,7 @@
         <v>1071</v>
       </c>
     </row>
-    <row r="358" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="358" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
       <c r="A358" s="1">
         <v>9315184408</v>
       </c>
@@ -10972,7 +10980,7 @@
         <v>1074</v>
       </c>
     </row>
-    <row r="359" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="359" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
       <c r="A359" s="1">
         <v>24164848855</v>
       </c>
@@ -10986,7 +10994,7 @@
         <v>1077</v>
       </c>
     </row>
-    <row r="360" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="360" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
       <c r="A360" s="1">
         <v>9869548881</v>
       </c>
@@ -11000,7 +11008,7 @@
         <v>1080</v>
       </c>
     </row>
-    <row r="361" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="361" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
       <c r="A361" s="1">
         <v>30131755838</v>
       </c>
@@ -11014,7 +11022,7 @@
         <v>1083</v>
       </c>
     </row>
-    <row r="362" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="362" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
       <c r="A362" s="1">
         <v>13843064806</v>
       </c>
@@ -11028,7 +11036,7 @@
         <v>1086</v>
       </c>
     </row>
-    <row r="363" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="363" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
       <c r="A363" s="1">
         <v>19907482870</v>
       </c>
@@ -11042,7 +11050,7 @@
         <v>1089</v>
       </c>
     </row>
-    <row r="364" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="364" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
       <c r="A364" s="1">
         <v>28757309833</v>
       </c>
@@ -11056,7 +11064,7 @@
         <v>1092</v>
       </c>
     </row>
-    <row r="365" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="365" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
       <c r="A365" s="1">
         <v>64310086500</v>
       </c>
@@ -11070,7 +11078,7 @@
         <v>1095</v>
       </c>
     </row>
-    <row r="366" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="366" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
       <c r="A366" s="1">
         <v>49843219899</v>
       </c>
@@ -11084,7 +11092,7 @@
         <v>1098</v>
       </c>
     </row>
-    <row r="367" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="367" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
       <c r="A367" s="1">
         <v>7249097881</v>
       </c>
@@ -11098,7 +11106,7 @@
         <v>1101</v>
       </c>
     </row>
-    <row r="368" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="368" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
       <c r="A368" s="1">
         <v>5915808964</v>
       </c>
@@ -11112,7 +11120,7 @@
         <v>1104</v>
       </c>
     </row>
-    <row r="369" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="369" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
       <c r="A369" s="1">
         <v>3747023495</v>
       </c>
@@ -11126,7 +11134,7 @@
         <v>1107</v>
       </c>
     </row>
-    <row r="370" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="370" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
       <c r="A370" s="1">
         <v>1939944880</v>
       </c>
@@ -11136,11 +11144,11 @@
       <c r="C370" s="2" t="s">
         <v>1109</v>
       </c>
-      <c r="D370" s="2" t="s">
+      <c r="D370" s="3" t="s">
         <v>1110</v>
       </c>
     </row>
-    <row r="371" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="371" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
       <c r="A371" s="1">
         <v>2562696379</v>
       </c>
@@ -11154,7 +11162,7 @@
         <v>1113</v>
       </c>
     </row>
-    <row r="372" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="372" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
       <c r="A372" s="1">
         <v>16775948883</v>
       </c>
@@ -11168,7 +11176,7 @@
         <v>1116</v>
       </c>
     </row>
-    <row r="373" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="373" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
       <c r="A373" s="1">
         <v>19926056881</v>
       </c>
@@ -11182,7 +11190,7 @@
         <v>1119</v>
       </c>
     </row>
-    <row r="374" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="374" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
       <c r="A374" s="1">
         <v>51882032861</v>
       </c>
@@ -11196,7 +11204,7 @@
         <v>1122</v>
       </c>
     </row>
-    <row r="375" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="375" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
       <c r="A375" s="1">
         <v>9868815894</v>
       </c>
@@ -11210,7 +11218,7 @@
         <v>1125</v>
       </c>
     </row>
-    <row r="376" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="376" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
       <c r="A376" s="1">
         <v>43111943828</v>
       </c>
@@ -11224,7 +11232,7 @@
         <v>1128</v>
       </c>
     </row>
-    <row r="377" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="377" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
       <c r="A377" s="1">
         <v>10971473803</v>
       </c>
@@ -11238,7 +11246,7 @@
         <v>1131</v>
       </c>
     </row>
-    <row r="378" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="378" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
       <c r="A378" s="1">
         <v>9850959894</v>
       </c>
@@ -11252,7 +11260,7 @@
         <v>1134</v>
       </c>
     </row>
-    <row r="379" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="379" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
       <c r="A379" s="1">
         <v>6929465437</v>
       </c>
@@ -11266,7 +11274,7 @@
         <v>1137</v>
       </c>
     </row>
-    <row r="380" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="380" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
       <c r="A380" s="1">
         <v>5787972830</v>
       </c>
@@ -11280,7 +11288,7 @@
         <v>1140</v>
       </c>
     </row>
-    <row r="381" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="381" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
       <c r="A381" s="1">
         <v>28810011813</v>
       </c>
@@ -11294,7 +11302,7 @@
         <v>1143</v>
       </c>
     </row>
-    <row r="382" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="382" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
       <c r="A382" s="1">
         <v>3482500371</v>
       </c>
@@ -11308,7 +11316,7 @@
         <v>1146</v>
       </c>
     </row>
-    <row r="383" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="383" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
       <c r="A383" s="1">
         <v>26747622847</v>
       </c>
@@ -11322,7 +11330,7 @@
         <v>1149</v>
       </c>
     </row>
-    <row r="384" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="384" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
       <c r="A384" s="1">
         <v>15017090894</v>
       </c>
@@ -11336,7 +11344,7 @@
         <v>1152</v>
       </c>
     </row>
-    <row r="385" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="385" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
       <c r="A385" s="1">
         <v>45642579860</v>
       </c>
@@ -11350,7 +11358,7 @@
         <v>1155</v>
       </c>
     </row>
-    <row r="386" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="386" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
       <c r="A386" s="1">
         <v>18564736861</v>
       </c>
@@ -11364,7 +11372,7 @@
         <v>1158</v>
       </c>
     </row>
-    <row r="387" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="387" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
       <c r="A387" s="1">
         <v>25479233866</v>
       </c>
@@ -11378,7 +11386,7 @@
         <v>1161</v>
       </c>
     </row>
-    <row r="388" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="388" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
       <c r="A388" s="1">
         <v>12195716878</v>
       </c>
@@ -11392,7 +11400,7 @@
         <v>1164</v>
       </c>
     </row>
-    <row r="389" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="389" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
       <c r="A389" s="1">
         <v>12208202880</v>
       </c>
@@ -11406,7 +11414,7 @@
         <v>1167</v>
       </c>
     </row>
-    <row r="390" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="390" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
       <c r="A390" s="1">
         <v>12202873856</v>
       </c>
@@ -11420,7 +11428,7 @@
         <v>1170</v>
       </c>
     </row>
-    <row r="391" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="391" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
       <c r="A391" s="1">
         <v>20993948812</v>
       </c>
@@ -11434,7 +11442,7 @@
         <v>1173</v>
       </c>
     </row>
-    <row r="392" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="392" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
       <c r="A392" s="1">
         <v>21698463871</v>
       </c>
@@ -11448,7 +11456,7 @@
         <v>1176</v>
       </c>
     </row>
-    <row r="393" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="393" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
       <c r="A393" s="1">
         <v>51606602837</v>
       </c>
@@ -11462,7 +11470,7 @@
         <v>1179</v>
       </c>
     </row>
-    <row r="394" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="394" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
       <c r="A394" s="1">
         <v>33781008851</v>
       </c>
@@ -11476,7 +11484,7 @@
         <v>1182</v>
       </c>
     </row>
-    <row r="395" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="395" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
       <c r="A395" s="1">
         <v>47919781884</v>
       </c>
@@ -11490,7 +11498,7 @@
         <v>1185</v>
       </c>
     </row>
-    <row r="396" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="396" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
       <c r="A396" s="1">
         <v>38418682825</v>
       </c>
@@ -11504,7 +11512,7 @@
         <v>1188</v>
       </c>
     </row>
-    <row r="397" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="397" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
       <c r="A397" s="1">
         <v>32406540839</v>
       </c>
@@ -11518,7 +11526,7 @@
         <v>1191</v>
       </c>
     </row>
-    <row r="398" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="398" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
       <c r="A398" s="1">
         <v>20990425860</v>
       </c>
@@ -11532,7 +11540,7 @@
         <v>1194</v>
       </c>
     </row>
-    <row r="399" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="399" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
       <c r="A399" s="1">
         <v>12196264814</v>
       </c>
@@ -11546,7 +11554,7 @@
         <v>1197</v>
       </c>
     </row>
-    <row r="400" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="400" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
       <c r="A400" s="1">
         <v>2547781603</v>
       </c>
@@ -11560,7 +11568,7 @@
         <v>1200</v>
       </c>
     </row>
-    <row r="401" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="401" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
       <c r="A401" s="1">
         <v>15021259865</v>
       </c>
@@ -11574,7 +11582,7 @@
         <v>1203</v>
       </c>
     </row>
-    <row r="402" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="402" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
       <c r="A402" s="1">
         <v>36021855833</v>
       </c>
@@ -11588,7 +11596,7 @@
         <v>1206</v>
       </c>
     </row>
-    <row r="403" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="403" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
       <c r="A403" s="1">
         <v>42107063885</v>
       </c>
@@ -11602,7 +11610,7 @@
         <v>1209</v>
       </c>
     </row>
-    <row r="404" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="404" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
       <c r="A404" s="1">
         <v>13836123827</v>
       </c>
@@ -11616,7 +11624,7 @@
         <v>1212</v>
       </c>
     </row>
-    <row r="405" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="405" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
       <c r="A405" s="1">
         <v>41148179801</v>
       </c>
@@ -11630,7 +11638,7 @@
         <v>1215</v>
       </c>
     </row>
-    <row r="406" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="406" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
       <c r="A406" s="1">
         <v>35060834816</v>
       </c>
@@ -11644,7 +11652,7 @@
         <v>1218</v>
       </c>
     </row>
-    <row r="407" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="407" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
       <c r="A407" s="1">
         <v>48079986843</v>
       </c>
@@ -11658,7 +11666,7 @@
         <v>1221</v>
       </c>
     </row>
-    <row r="408" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="408" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
       <c r="A408" s="1">
         <v>15017254838</v>
       </c>
@@ -11672,7 +11680,7 @@
         <v>1224</v>
       </c>
     </row>
-    <row r="409" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="409" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
       <c r="A409" s="1">
         <v>24319932803</v>
       </c>
@@ -11686,7 +11694,7 @@
         <v>1227</v>
       </c>
     </row>
-    <row r="410" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="410" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
       <c r="A410" s="1">
         <v>29042374888</v>
       </c>
@@ -11700,7 +11708,7 @@
         <v>1230</v>
       </c>
     </row>
-    <row r="411" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="411" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
       <c r="A411" s="1">
         <v>47800074889</v>
       </c>
@@ -11714,7 +11722,7 @@
         <v>1233</v>
       </c>
     </row>
-    <row r="412" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="412" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
       <c r="A412" s="1">
         <v>59752371817</v>
       </c>
@@ -11728,7 +11736,7 @@
         <v>1236</v>
       </c>
     </row>
-    <row r="413" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="413" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
       <c r="A413" s="1">
         <v>5794303832</v>
       </c>
@@ -11742,7 +11750,7 @@
         <v>1239</v>
       </c>
     </row>
-    <row r="414" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="414" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
       <c r="A414" s="1">
         <v>42704258813</v>
       </c>
@@ -11756,7 +11764,7 @@
         <v>1242</v>
       </c>
     </row>
-    <row r="415" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="415" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
       <c r="A415" s="1">
         <v>31015526802</v>
       </c>
@@ -11770,7 +11778,7 @@
         <v>1245</v>
       </c>
     </row>
-    <row r="416" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="416" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
       <c r="A416" s="1">
         <v>12203870885</v>
       </c>
@@ -11784,7 +11792,7 @@
         <v>1248</v>
       </c>
     </row>
-    <row r="417" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="417" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
       <c r="A417" s="1">
         <v>7403204670</v>
       </c>
@@ -11798,7 +11806,7 @@
         <v>1251</v>
       </c>
     </row>
-    <row r="418" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="418" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
       <c r="A418" s="1">
         <v>48392091892</v>
       </c>
@@ -11812,7 +11820,7 @@
         <v>1254</v>
       </c>
     </row>
-    <row r="419" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="419" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
       <c r="A419" s="1">
         <v>34863673825</v>
       </c>
@@ -11826,7 +11834,7 @@
         <v>1257</v>
       </c>
     </row>
-    <row r="420" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="420" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
       <c r="A420" s="1">
         <v>24786199893</v>
       </c>
@@ -11840,7 +11848,7 @@
         <v>1260</v>
       </c>
     </row>
-    <row r="421" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="421" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
       <c r="A421" s="1">
         <v>12202381805</v>
       </c>
@@ -11854,7 +11862,7 @@
         <v>1263</v>
       </c>
     </row>
-    <row r="422" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="422" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
       <c r="A422" s="1">
         <v>40347498817</v>
       </c>
@@ -11868,7 +11876,7 @@
         <v>1266</v>
       </c>
     </row>
-    <row r="423" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="423" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
       <c r="A423" s="1">
         <v>58956819807</v>
       </c>
@@ -11882,7 +11890,7 @@
         <v>1269</v>
       </c>
     </row>
-    <row r="424" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="424" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
       <c r="A424" s="1">
         <v>43761407831</v>
       </c>
@@ -11896,7 +11904,7 @@
         <v>1272</v>
       </c>
     </row>
-    <row r="425" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="425" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
       <c r="A425" s="1">
         <v>43980743845</v>
       </c>
@@ -11910,7 +11918,7 @@
         <v>1275</v>
       </c>
     </row>
-    <row r="426" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="426" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
       <c r="A426" s="1">
         <v>46453511843</v>
       </c>
@@ -11924,7 +11932,7 @@
         <v>1278</v>
       </c>
     </row>
-    <row r="427" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="427" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
       <c r="A427" s="1">
         <v>42502897882</v>
       </c>
@@ -11938,7 +11946,7 @@
         <v>1281</v>
       </c>
     </row>
-    <row r="428" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="428" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
       <c r="A428" s="1">
         <v>42075150893</v>
       </c>
@@ -11952,7 +11960,7 @@
         <v>1284</v>
       </c>
     </row>
-    <row r="429" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="429" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
       <c r="A429" s="1">
         <v>42033722830</v>
       </c>
@@ -11966,7 +11974,7 @@
         <v>1287</v>
       </c>
     </row>
-    <row r="430" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="430" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
       <c r="A430" s="1">
         <v>51106891805</v>
       </c>
@@ -11980,7 +11988,7 @@
         <v>1290</v>
       </c>
     </row>
-    <row r="431" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="431" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
       <c r="A431" s="1">
         <v>48559801880</v>
       </c>
@@ -11994,7 +12002,7 @@
         <v>1293</v>
       </c>
     </row>
-    <row r="432" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="432" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
       <c r="A432" s="1">
         <v>42122352850</v>
       </c>
@@ -12008,7 +12016,7 @@
         <v>1296</v>
       </c>
     </row>
-    <row r="433" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="433" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
       <c r="A433" s="1">
         <v>37193211854</v>
       </c>
@@ -12022,7 +12030,7 @@
         <v>1299</v>
       </c>
     </row>
-    <row r="434" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="434" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
       <c r="A434" s="1">
         <v>37238151898</v>
       </c>
@@ -12036,7 +12044,7 @@
         <v>1302</v>
       </c>
     </row>
-    <row r="435" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="435" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
       <c r="A435" s="1">
         <v>18565881814</v>
       </c>
@@ -12050,7 +12058,7 @@
         <v>1305</v>
       </c>
     </row>
-    <row r="436" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="436" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
       <c r="A436" s="1">
         <v>15007831883</v>
       </c>
@@ -12064,7 +12072,7 @@
         <v>1308</v>
       </c>
     </row>
-    <row r="437" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="437" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
       <c r="A437" s="1">
         <v>54779559880</v>
       </c>
@@ -12078,7 +12086,7 @@
         <v>1311</v>
       </c>
     </row>
-    <row r="438" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="438" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
       <c r="A438" s="1">
         <v>33430221870</v>
       </c>
@@ -12092,7 +12100,7 @@
         <v>1314</v>
       </c>
     </row>
-    <row r="439" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="439" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
       <c r="A439" s="1">
         <v>5027878800</v>
       </c>
@@ -12106,7 +12114,7 @@
         <v>1317</v>
       </c>
     </row>
-    <row r="440" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="440" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
       <c r="A440" s="1">
         <v>26035803881</v>
       </c>
@@ -12120,7 +12128,7 @@
         <v>1320</v>
       </c>
     </row>
-    <row r="441" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="441" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
       <c r="A441" s="1">
         <v>13223487824</v>
       </c>
@@ -12134,7 +12142,7 @@
         <v>1323</v>
       </c>
     </row>
-    <row r="442" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="442" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
       <c r="A442" s="1">
         <v>44346275893</v>
       </c>
@@ -12148,7 +12156,7 @@
         <v>1326</v>
       </c>
     </row>
-    <row r="443" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="443" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
       <c r="A443" s="1">
         <v>2602925837</v>
       </c>
@@ -12162,7 +12170,7 @@
         <v>1329</v>
       </c>
     </row>
-    <row r="444" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="444" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
       <c r="A444" s="1">
         <v>9870086845</v>
       </c>
@@ -12176,7 +12184,7 @@
         <v>1332</v>
       </c>
     </row>
-    <row r="445" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="445" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
       <c r="A445" s="1">
         <v>45495745850</v>
       </c>
@@ -12190,7 +12198,7 @@
         <v>1335</v>
       </c>
     </row>
-    <row r="446" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="446" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
       <c r="A446" s="1">
         <v>44546931883</v>
       </c>
@@ -12204,7 +12212,7 @@
         <v>1338</v>
       </c>
     </row>
-    <row r="447" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="447" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
       <c r="A447" s="1">
         <v>42135992801</v>
       </c>
@@ -12218,7 +12226,7 @@
         <v>1341</v>
       </c>
     </row>
-    <row r="448" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="448" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
       <c r="A448" s="1">
         <v>34977153871</v>
       </c>
@@ -12232,7 +12240,7 @@
         <v>1344</v>
       </c>
     </row>
-    <row r="449" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="449" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
       <c r="A449" s="1">
         <v>15302739860</v>
       </c>
@@ -12246,7 +12254,7 @@
         <v>1347</v>
       </c>
     </row>
-    <row r="450" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="450" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
       <c r="A450" s="1">
         <v>31973837889</v>
       </c>
@@ -12260,7 +12268,7 @@
         <v>1350</v>
       </c>
     </row>
-    <row r="451" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="451" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
       <c r="A451" s="1">
         <v>33295048894</v>
       </c>
@@ -12274,7 +12282,7 @@
         <v>1353</v>
       </c>
     </row>
-    <row r="452" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="452" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
       <c r="A452" s="1">
         <v>37404277876</v>
       </c>
@@ -12288,7 +12296,7 @@
         <v>1356</v>
       </c>
     </row>
-    <row r="453" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="453" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
       <c r="A453" s="1">
         <v>12200525826</v>
       </c>
@@ -12302,7 +12310,7 @@
         <v>1359</v>
       </c>
     </row>
-    <row r="454" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="454" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
       <c r="A454" s="1">
         <v>35718411824</v>
       </c>
@@ -12316,7 +12324,7 @@
         <v>1362</v>
       </c>
     </row>
-    <row r="455" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="455" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
       <c r="A455" s="1">
         <v>39085101808</v>
       </c>
@@ -12330,7 +12338,7 @@
         <v>1365</v>
       </c>
     </row>
-    <row r="456" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="456" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
       <c r="A456" s="1">
         <v>18377693895</v>
       </c>
@@ -12344,7 +12352,7 @@
         <v>1368</v>
       </c>
     </row>
-    <row r="457" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="457" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
       <c r="A457" s="1">
         <v>9863323802</v>
       </c>
@@ -12358,7 +12366,7 @@
         <v>1371</v>
       </c>
     </row>
-    <row r="458" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="458" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
       <c r="A458" s="1">
         <v>5788841860</v>
       </c>
@@ -12372,7 +12380,7 @@
         <v>1374</v>
       </c>
     </row>
-    <row r="459" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="459" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
       <c r="A459" s="1">
         <v>36249685804</v>
       </c>
@@ -12386,7 +12394,7 @@
         <v>1377</v>
       </c>
     </row>
-    <row r="460" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="460" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
       <c r="A460" s="1">
         <v>31145292836</v>
       </c>
@@ -12400,7 +12408,7 @@
         <v>1380</v>
       </c>
     </row>
-    <row r="461" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="461" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
       <c r="A461" s="1">
         <v>11321540817</v>
       </c>
@@ -12414,7 +12422,7 @@
         <v>1383</v>
       </c>
     </row>
-    <row r="462" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="462" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
       <c r="A462" s="1">
         <v>266528899</v>
       </c>
@@ -12428,7 +12436,7 @@
         <v>1386</v>
       </c>
     </row>
-    <row r="463" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="463" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
       <c r="A463" s="1">
         <v>38538654888</v>
       </c>
@@ -12442,7 +12450,7 @@
         <v>1389</v>
       </c>
     </row>
-    <row r="464" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="464" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
       <c r="A464" s="1">
         <v>37616009840</v>
       </c>
@@ -12456,7 +12464,7 @@
         <v>1392</v>
       </c>
     </row>
-    <row r="465" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="465" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
       <c r="A465" s="1">
         <v>59930392807</v>
       </c>
@@ -12470,7 +12478,7 @@
         <v>1395</v>
       </c>
     </row>
-    <row r="466" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="466" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
       <c r="A466" s="1">
         <v>40826492800</v>
       </c>
@@ -12484,7 +12492,7 @@
         <v>1398</v>
       </c>
     </row>
-    <row r="467" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="467" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
       <c r="A467" s="1">
         <v>40872144860</v>
       </c>
@@ -12498,7 +12506,7 @@
         <v>1401</v>
       </c>
     </row>
-    <row r="468" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="468" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
       <c r="A468" s="1">
         <v>38744859864</v>
       </c>
@@ -12512,7 +12520,7 @@
         <v>1404</v>
       </c>
     </row>
-    <row r="469" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="469" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
       <c r="A469" s="1">
         <v>40380883830</v>
       </c>
@@ -12526,7 +12534,7 @@
         <v>1407</v>
       </c>
     </row>
-    <row r="470" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="470" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
       <c r="A470" s="1">
         <v>36573597885</v>
       </c>
@@ -12540,7 +12548,7 @@
         <v>1410</v>
       </c>
     </row>
-    <row r="471" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="471" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
       <c r="A471" s="1">
         <v>34341887890</v>
       </c>
@@ -12554,7 +12562,7 @@
         <v>1413</v>
       </c>
     </row>
-    <row r="472" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="472" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
       <c r="A472" s="1">
         <v>20990192822</v>
       </c>
@@ -12568,7 +12576,7 @@
         <v>1416</v>
       </c>
     </row>
-    <row r="473" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="473" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
       <c r="A473" s="1">
         <v>43322397840</v>
       </c>
@@ -12582,7 +12590,7 @@
         <v>1419</v>
       </c>
     </row>
-    <row r="474" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="474" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
       <c r="A474" s="1">
         <v>44950323806</v>
       </c>
@@ -12596,7 +12604,7 @@
         <v>1422</v>
       </c>
     </row>
-    <row r="475" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="475" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
       <c r="A475" s="1">
         <v>1288388500</v>
       </c>
@@ -12610,7 +12618,7 @@
         <v>1425</v>
       </c>
     </row>
-    <row r="476" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="476" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
       <c r="A476" s="1">
         <v>23992340813</v>
       </c>
@@ -12624,7 +12632,7 @@
         <v>1428</v>
       </c>
     </row>
-    <row r="477" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="477" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
       <c r="A477" s="1">
         <v>51725104865</v>
       </c>
@@ -12638,7 +12646,7 @@
         <v>1431</v>
       </c>
     </row>
-    <row r="478" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="478" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
       <c r="A478" s="1">
         <v>36100611899</v>
       </c>
@@ -12652,7 +12660,7 @@
         <v>1434</v>
       </c>
     </row>
-    <row r="479" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="479" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
       <c r="A479" s="1">
         <v>45215297800</v>
       </c>
@@ -12666,7 +12674,7 @@
         <v>1437</v>
       </c>
     </row>
-    <row r="480" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="480" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
       <c r="A480" s="1">
         <v>43270781822</v>
       </c>
@@ -12680,7 +12688,7 @@
         <v>1440</v>
       </c>
     </row>
-    <row r="481" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="481" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
       <c r="A481" s="1">
         <v>47601057860</v>
       </c>
@@ -12694,7 +12702,7 @@
         <v>1443</v>
       </c>
     </row>
-    <row r="482" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="482" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
       <c r="A482" s="1">
         <v>31256773867</v>
       </c>
@@ -12708,7 +12716,7 @@
         <v>1446</v>
       </c>
     </row>
-    <row r="483" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="483" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
       <c r="A483" s="1">
         <v>21422287807</v>
       </c>
@@ -12722,7 +12730,7 @@
         <v>1449</v>
       </c>
     </row>
-    <row r="484" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="484" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
       <c r="A484" s="1">
         <v>35912390896</v>
       </c>
@@ -12736,7 +12744,7 @@
         <v>1452</v>
       </c>
     </row>
-    <row r="485" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="485" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
       <c r="A485" s="1">
         <v>5788128862</v>
       </c>
@@ -12750,7 +12758,7 @@
         <v>1455</v>
       </c>
     </row>
-    <row r="486" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="486" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
       <c r="A486" s="1">
         <v>3348647800</v>
       </c>
@@ -12764,7 +12772,7 @@
         <v>1458</v>
       </c>
     </row>
-    <row r="487" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="487" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
       <c r="A487" s="1">
         <v>37568735877</v>
       </c>
@@ -12778,7 +12786,7 @@
         <v>1461</v>
       </c>
     </row>
-    <row r="488" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="488" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
       <c r="A488" s="1">
         <v>22197193830</v>
       </c>
@@ -12792,7 +12800,7 @@
         <v>1464</v>
       </c>
     </row>
-    <row r="489" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="489" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
       <c r="A489" s="1">
         <v>24170642864</v>
       </c>
@@ -12806,7 +12814,7 @@
         <v>1467</v>
       </c>
     </row>
-    <row r="490" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="490" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
       <c r="A490" s="1">
         <v>22523186861</v>
       </c>
@@ -12820,7 +12828,7 @@
         <v>1470</v>
       </c>
     </row>
-    <row r="491" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="491" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
       <c r="A491" s="1">
         <v>13838381866</v>
       </c>
@@ -12834,7 +12842,7 @@
         <v>1473</v>
       </c>
     </row>
-    <row r="492" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="492" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
       <c r="A492" s="1">
         <v>19916385823</v>
       </c>
@@ -12848,7 +12856,7 @@
         <v>1476</v>
       </c>
     </row>
-    <row r="493" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="493" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
       <c r="A493" s="1">
         <v>10676208851</v>
       </c>
@@ -12862,7 +12870,7 @@
         <v>1479</v>
       </c>
     </row>
-    <row r="494" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="494" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
       <c r="A494" s="1">
         <v>29309935880</v>
       </c>
@@ -12876,7 +12884,7 @@
         <v>1482</v>
       </c>
     </row>
-    <row r="495" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="495" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
       <c r="A495" s="1">
         <v>14474577817</v>
       </c>
@@ -12890,7 +12898,7 @@
         <v>1485</v>
       </c>
     </row>
-    <row r="496" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="496" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
       <c r="A496" s="1">
         <v>37926298875</v>
       </c>
@@ -12904,7 +12912,7 @@
         <v>1488</v>
       </c>
     </row>
-    <row r="497" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="497" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
       <c r="A497" s="1">
         <v>10970271808</v>
       </c>
@@ -12918,7 +12926,7 @@
         <v>1491</v>
       </c>
     </row>
-    <row r="498" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="498" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
       <c r="A498" s="1">
         <v>12202483802</v>
       </c>
@@ -12932,7 +12940,7 @@
         <v>1494</v>
       </c>
     </row>
-    <row r="499" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="499" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
       <c r="A499" s="1">
         <v>12213581894</v>
       </c>
@@ -12946,7 +12954,7 @@
         <v>1497</v>
       </c>
     </row>
-    <row r="500" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="500" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
       <c r="A500" s="1">
         <v>42956920855</v>
       </c>
@@ -12960,7 +12968,7 @@
         <v>1500</v>
       </c>
     </row>
-    <row r="501" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="501" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
       <c r="A501" s="1">
         <v>7239003884</v>
       </c>
@@ -12974,7 +12982,7 @@
         <v>1503</v>
       </c>
     </row>
-    <row r="502" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="502" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
       <c r="A502" s="1">
         <v>36268748859</v>
       </c>
@@ -12988,7 +12996,7 @@
         <v>1506</v>
       </c>
     </row>
-    <row r="503" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="503" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
       <c r="A503" s="1">
         <v>9846309880</v>
       </c>
@@ -13002,7 +13010,7 @@
         <v>1509</v>
       </c>
     </row>
-    <row r="504" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="504" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
       <c r="A504" s="1">
         <v>19906892803</v>
       </c>
@@ -13016,7 +13024,7 @@
         <v>1512</v>
       </c>
     </row>
-    <row r="505" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="505" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
       <c r="A505" s="1">
         <v>31975272838</v>
       </c>
@@ -13030,7 +13038,7 @@
         <v>1515</v>
       </c>
     </row>
-    <row r="506" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="506" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
       <c r="A506" s="1">
         <v>8289162847</v>
       </c>
@@ -13044,7 +13052,7 @@
         <v>1518</v>
       </c>
     </row>
-    <row r="507" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="507" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
       <c r="A507" s="1">
         <v>35054354816</v>
       </c>
@@ -13058,7 +13066,7 @@
         <v>1521</v>
       </c>
     </row>
-    <row r="508" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="508" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
       <c r="A508" s="1">
         <v>94081700320</v>
       </c>
@@ -13072,7 +13080,7 @@
         <v>1524</v>
       </c>
     </row>
-    <row r="509" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="509" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
       <c r="A509" s="1">
         <v>33953864491</v>
       </c>
@@ -13086,7 +13094,7 @@
         <v>1527</v>
       </c>
     </row>
-    <row r="510" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="510" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
       <c r="A510" s="1">
         <v>30698733835</v>
       </c>
@@ -13100,7 +13108,7 @@
         <v>1530</v>
       </c>
     </row>
-    <row r="511" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="511" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
       <c r="A511" s="1">
         <v>19925676894</v>
       </c>
@@ -13114,7 +13122,7 @@
         <v>1533</v>
       </c>
     </row>
-    <row r="512" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="512" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
       <c r="A512" s="1">
         <v>38030213832</v>
       </c>
@@ -13128,7 +13136,7 @@
         <v>1536</v>
       </c>
     </row>
-    <row r="513" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="513" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
       <c r="A513" s="1">
         <v>32556430826</v>
       </c>
@@ -13142,7 +13150,7 @@
         <v>1539</v>
       </c>
     </row>
-    <row r="514" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="514" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
       <c r="A514" s="1">
         <v>17859155842</v>
       </c>
@@ -13156,7 +13164,7 @@
         <v>1542</v>
       </c>
     </row>
-    <row r="515" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="515" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
       <c r="A515" s="1">
         <v>33661242881</v>
       </c>
@@ -13170,7 +13178,7 @@
         <v>1545</v>
       </c>
     </row>
-    <row r="516" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="516" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
       <c r="A516" s="1">
         <v>8116966855</v>
       </c>
@@ -13184,7 +13192,7 @@
         <v>1548</v>
       </c>
     </row>
-    <row r="517" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="517" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
       <c r="A517" s="1">
         <v>35443932802</v>
       </c>
@@ -13198,7 +13206,7 @@
         <v>1551</v>
       </c>
     </row>
-    <row r="518" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="518" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
       <c r="A518" s="1">
         <v>24324847894</v>
       </c>
@@ -13212,7 +13220,7 @@
         <v>1554</v>
       </c>
     </row>
-    <row r="519" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="519" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
       <c r="A519" s="1">
         <v>38978286852</v>
       </c>
@@ -13226,7 +13234,7 @@
         <v>1557</v>
       </c>
     </row>
-    <row r="520" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="520" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
       <c r="A520" s="1">
         <v>15017517863</v>
       </c>
@@ -13240,7 +13248,7 @@
         <v>1560</v>
       </c>
     </row>
-    <row r="521" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="521" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
       <c r="A521" s="1">
         <v>9160218827</v>
       </c>
@@ -13254,7 +13262,7 @@
         <v>1563</v>
       </c>
     </row>
-    <row r="522" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="522" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
       <c r="A522" s="1">
         <v>10973344814</v>
       </c>
@@ -13268,7 +13276,7 @@
         <v>1566</v>
       </c>
     </row>
-    <row r="523" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="523" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
       <c r="A523" s="1">
         <v>12213097810</v>
       </c>
@@ -13282,7 +13290,7 @@
         <v>1569</v>
       </c>
     </row>
-    <row r="524" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="524" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
       <c r="A524" s="1">
         <v>27440500830</v>
       </c>
@@ -13296,7 +13304,7 @@
         <v>1572</v>
       </c>
     </row>
-    <row r="525" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="525" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
       <c r="A525" s="1">
         <v>4364447803</v>
       </c>
@@ -13310,7 +13318,7 @@
         <v>1575</v>
       </c>
     </row>
-    <row r="526" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="526" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
       <c r="A526" s="1">
         <v>36184553801</v>
       </c>
@@ -13324,7 +13332,7 @@
         <v>1578</v>
       </c>
     </row>
-    <row r="527" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="527" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
       <c r="A527" s="1">
         <v>25260892801</v>
       </c>
@@ -13338,7 +13346,7 @@
         <v>1581</v>
       </c>
     </row>
-    <row r="528" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="528" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
       <c r="A528" s="1">
         <v>49585113856</v>
       </c>
@@ -13352,7 +13360,7 @@
         <v>1584</v>
       </c>
     </row>
-    <row r="529" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="529" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
       <c r="A529" s="1">
         <v>7232450885</v>
       </c>
@@ -13366,7 +13374,7 @@
         <v>1587</v>
       </c>
     </row>
-    <row r="530" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="530" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
       <c r="A530" s="1">
         <v>37513004811</v>
       </c>
@@ -13380,7 +13388,7 @@
         <v>1590</v>
       </c>
     </row>
-    <row r="531" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="531" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
       <c r="A531" s="1">
         <v>8120868803</v>
       </c>
@@ -13394,7 +13402,7 @@
         <v>1593</v>
       </c>
     </row>
-    <row r="532" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="532" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
       <c r="A532" s="1">
         <v>18565989852</v>
       </c>
@@ -13408,7 +13416,7 @@
         <v>1596</v>
       </c>
     </row>
-    <row r="533" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="533" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
       <c r="A533" s="1">
         <v>21387790846</v>
       </c>
@@ -13422,7 +13430,7 @@
         <v>1599</v>
       </c>
     </row>
-    <row r="534" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="534" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
       <c r="A534" s="1">
         <v>38070738847</v>
       </c>
@@ -13436,7 +13444,7 @@
         <v>1602</v>
       </c>
     </row>
-    <row r="535" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="535" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
       <c r="A535" s="1">
         <v>28050899870</v>
       </c>
@@ -13450,7 +13458,7 @@
         <v>1605</v>
       </c>
     </row>
-    <row r="536" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="536" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
       <c r="A536" s="1">
         <v>15947754860</v>
       </c>
@@ -13464,7 +13472,7 @@
         <v>1608</v>
       </c>
     </row>
-    <row r="537" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="537" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
       <c r="A537" s="1">
         <v>12194346805</v>
       </c>
@@ -13478,7 +13486,7 @@
         <v>1611</v>
       </c>
     </row>
-    <row r="538" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="538" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
       <c r="A538" s="1">
         <v>14474809882</v>
       </c>
@@ -13492,7 +13500,7 @@
         <v>1614</v>
       </c>
     </row>
-    <row r="539" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="539" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
       <c r="A539" s="1">
         <v>39492810883</v>
       </c>
@@ -13506,7 +13514,7 @@
         <v>1617</v>
       </c>
     </row>
-    <row r="540" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="540" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
       <c r="A540" s="1">
         <v>12200053800</v>
       </c>
@@ -13520,7 +13528,7 @@
         <v>1620</v>
       </c>
     </row>
-    <row r="541" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="541" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
       <c r="A541" s="1">
         <v>22201923850</v>
       </c>
@@ -13534,7 +13542,7 @@
         <v>1623</v>
       </c>
     </row>
-    <row r="542" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="542" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
       <c r="A542" s="1">
         <v>14476321844</v>
       </c>
@@ -13548,7 +13556,7 @@
         <v>1626</v>
       </c>
     </row>
-    <row r="543" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="543" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
       <c r="A543" s="1">
         <v>12213987840</v>
       </c>
@@ -13562,7 +13570,7 @@
         <v>1629</v>
       </c>
     </row>
-    <row r="544" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="544" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
       <c r="A544" s="1">
         <v>33371029808</v>
       </c>
@@ -13576,7 +13584,7 @@
         <v>1632</v>
       </c>
     </row>
-    <row r="545" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="545" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
       <c r="A545" s="1">
         <v>32706063890</v>
       </c>
@@ -13590,7 +13598,7 @@
         <v>1635</v>
       </c>
     </row>
-    <row r="546" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="546" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
       <c r="A546" s="1">
         <v>27161377811</v>
       </c>
@@ -13604,7 +13612,7 @@
         <v>1638</v>
       </c>
     </row>
-    <row r="547" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="547" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
       <c r="A547" s="1">
         <v>41239290870</v>
       </c>
@@ -13618,7 +13626,7 @@
         <v>1641</v>
       </c>
     </row>
-    <row r="548" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="548" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
       <c r="A548" s="1">
         <v>23284977805</v>
       </c>
@@ -13632,7 +13640,7 @@
         <v>1644</v>
       </c>
     </row>
-    <row r="549" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="549" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
       <c r="A549" s="1">
         <v>3868110402</v>
       </c>
@@ -13646,7 +13654,7 @@
         <v>1647</v>
       </c>
     </row>
-    <row r="550" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="550" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
       <c r="A550" s="1">
         <v>10758307888</v>
       </c>
@@ -13660,7 +13668,7 @@
         <v>1650</v>
       </c>
     </row>
-    <row r="551" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="551" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
       <c r="A551" s="1">
         <v>12195994843</v>
       </c>
@@ -13674,7 +13682,7 @@
         <v>1653</v>
       </c>
     </row>
-    <row r="552" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="552" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
       <c r="A552" s="1">
         <v>21638230838</v>
       </c>
@@ -13688,7 +13696,7 @@
         <v>1656</v>
       </c>
     </row>
-    <row r="553" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="553" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
       <c r="A553" s="1">
         <v>57297025828</v>
       </c>
@@ -13702,7 +13710,7 @@
         <v>1659</v>
       </c>
     </row>
-    <row r="554" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="554" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
       <c r="A554" s="1">
         <v>40584589840</v>
       </c>
@@ -13716,7 +13724,7 @@
         <v>1662</v>
       </c>
     </row>
-    <row r="555" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="555" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
       <c r="A555" s="1">
         <v>12199547809</v>
       </c>
@@ -13730,7 +13738,7 @@
         <v>1665</v>
       </c>
     </row>
-    <row r="556" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="556" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
       <c r="A556" s="1">
         <v>36750343805</v>
       </c>
@@ -13744,7 +13752,7 @@
         <v>1668</v>
       </c>
     </row>
-    <row r="557" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="557" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
       <c r="A557" s="1">
         <v>29311445843</v>
       </c>
@@ -13758,7 +13766,7 @@
         <v>1671</v>
       </c>
     </row>
-    <row r="558" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="558" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
       <c r="A558" s="1">
         <v>40168810808</v>
       </c>
@@ -13772,7 +13780,7 @@
         <v>1674</v>
       </c>
     </row>
-    <row r="559" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="559" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
       <c r="A559" s="1">
         <v>36324857808</v>
       </c>
@@ -13786,7 +13794,7 @@
         <v>1677</v>
       </c>
     </row>
-    <row r="560" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="560" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
       <c r="A560" s="1">
         <v>57693952810</v>
       </c>
@@ -13800,7 +13808,7 @@
         <v>1680</v>
       </c>
     </row>
-    <row r="561" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="561" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
       <c r="A561" s="1">
         <v>33283437840</v>
       </c>
@@ -13814,7 +13822,7 @@
         <v>1683</v>
       </c>
     </row>
-    <row r="562" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="562" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
       <c r="A562" s="1">
         <v>28470254804</v>
       </c>
@@ -13828,7 +13836,7 @@
         <v>1686</v>
       </c>
     </row>
-    <row r="563" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="563" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
       <c r="A563" s="1">
         <v>39475845801</v>
       </c>
@@ -13842,7 +13850,7 @@
         <v>1689</v>
       </c>
     </row>
-    <row r="564" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="564" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
       <c r="A564" s="1">
         <v>10982894716</v>
       </c>
@@ -13856,7 +13864,7 @@
         <v>1692</v>
       </c>
     </row>
-    <row r="565" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="565" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
       <c r="A565" s="1">
         <v>45144372805</v>
       </c>
@@ -13870,7 +13878,7 @@
         <v>1695</v>
       </c>
     </row>
-    <row r="566" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="566" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
       <c r="A566" s="1">
         <v>47717140888</v>
       </c>
@@ -13884,7 +13892,7 @@
         <v>1698</v>
       </c>
     </row>
-    <row r="567" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="567" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
       <c r="A567" s="1">
         <v>24188822848</v>
       </c>
@@ -13898,7 +13906,7 @@
         <v>1701</v>
       </c>
     </row>
-    <row r="568" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="568" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
       <c r="A568" s="1">
         <v>49663406836</v>
       </c>
@@ -13912,7 +13920,7 @@
         <v>1704</v>
       </c>
     </row>
-    <row r="569" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="569" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
       <c r="A569" s="1">
         <v>37151719876</v>
       </c>
@@ -13926,7 +13934,7 @@
         <v>1707</v>
       </c>
     </row>
-    <row r="570" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="570" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
       <c r="A570" s="1">
         <v>25517274803</v>
       </c>
@@ -13940,7 +13948,7 @@
         <v>1710</v>
       </c>
     </row>
-    <row r="571" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="571" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
       <c r="A571" s="1">
         <v>34089649803</v>
       </c>
@@ -13954,7 +13962,7 @@
         <v>1713</v>
       </c>
     </row>
-    <row r="572" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="572" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
       <c r="A572" s="1">
         <v>29763772869</v>
       </c>
@@ -13968,7 +13976,7 @@
         <v>1716</v>
       </c>
     </row>
-    <row r="573" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="573" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
       <c r="A573" s="1">
         <v>29508232897</v>
       </c>
@@ -13982,7 +13990,7 @@
         <v>1719</v>
       </c>
     </row>
-    <row r="574" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="574" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
       <c r="A574" s="1">
         <v>9560460889</v>
       </c>
@@ -13996,7 +14004,7 @@
         <v>1722</v>
       </c>
     </row>
-    <row r="575" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="575" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
       <c r="A575" s="1">
         <v>34058482885</v>
       </c>
@@ -14010,7 +14018,7 @@
         <v>1725</v>
       </c>
     </row>
-    <row r="576" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="576" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
       <c r="A576" s="1">
         <v>9870271820</v>
       </c>
@@ -14024,7 +14032,7 @@
         <v>1728</v>
       </c>
     </row>
-    <row r="577" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="577" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
       <c r="A577" s="1">
         <v>21674475829</v>
       </c>
@@ -14038,7 +14046,7 @@
         <v>1731</v>
       </c>
     </row>
-    <row r="578" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="578" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
       <c r="A578" s="1">
         <v>19913285836</v>
       </c>
@@ -14052,7 +14060,7 @@
         <v>1734</v>
       </c>
     </row>
-    <row r="579" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="579" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
       <c r="A579" s="1">
         <v>21788372808</v>
       </c>
@@ -14066,7 +14074,7 @@
         <v>1737</v>
       </c>
     </row>
-    <row r="580" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="580" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
       <c r="A580" s="1">
         <v>18561865806</v>
       </c>
@@ -14080,7 +14088,7 @@
         <v>1740</v>
       </c>
     </row>
-    <row r="581" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="581" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
       <c r="A581" s="1">
         <v>9846100817</v>
       </c>
@@ -14094,7 +14102,7 @@
         <v>1743</v>
       </c>
     </row>
-    <row r="582" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="582" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
       <c r="A582" s="1">
         <v>28290559852</v>
       </c>
@@ -14108,7 +14116,7 @@
         <v>1746</v>
       </c>
     </row>
-    <row r="583" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="583" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
       <c r="A583" s="1">
         <v>35221591871</v>
       </c>
@@ -14122,7 +14130,7 @@
         <v>1749</v>
       </c>
     </row>
-    <row r="584" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="584" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
       <c r="A584" s="1">
         <v>29903071841</v>
       </c>
@@ -14136,7 +14144,7 @@
         <v>1752</v>
       </c>
     </row>
-    <row r="585" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="585" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
       <c r="A585" s="1">
         <v>40604068808</v>
       </c>
@@ -14150,7 +14158,7 @@
         <v>1755</v>
       </c>
     </row>
-    <row r="586" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="586" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
       <c r="A586" s="1">
         <v>31555678807</v>
       </c>
@@ -14164,7 +14172,7 @@
         <v>1758</v>
       </c>
     </row>
-    <row r="587" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="587" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
       <c r="A587" s="1">
         <v>19908933841</v>
       </c>
@@ -14178,7 +14186,7 @@
         <v>1761</v>
       </c>
     </row>
-    <row r="588" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="588" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
       <c r="A588" s="1">
         <v>26526794491</v>
       </c>
@@ -14192,7 +14200,7 @@
         <v>1764</v>
       </c>
     </row>
-    <row r="589" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="589" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
       <c r="A589" s="1">
         <v>12199530833</v>
       </c>
@@ -14206,7 +14214,7 @@
         <v>1767</v>
       </c>
     </row>
-    <row r="590" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="590" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
       <c r="A590" s="1">
         <v>34392607801</v>
       </c>
@@ -14220,7 +14228,7 @@
         <v>1770</v>
       </c>
     </row>
-    <row r="591" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="591" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
       <c r="A591" s="1">
         <v>12198694816</v>
       </c>
@@ -14234,7 +14242,7 @@
         <v>1773</v>
       </c>
     </row>
-    <row r="592" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="592" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
       <c r="A592" s="1">
         <v>79433642520</v>
       </c>
@@ -14248,7 +14256,7 @@
         <v>1776</v>
       </c>
     </row>
-    <row r="593" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="593" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
       <c r="A593" s="1">
         <v>43513537832</v>
       </c>
@@ -14262,7 +14270,7 @@
         <v>1779</v>
       </c>
     </row>
-    <row r="594" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="594" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
       <c r="A594" s="1">
         <v>43761234805</v>
       </c>
@@ -14276,7 +14284,7 @@
         <v>1782</v>
       </c>
     </row>
-    <row r="595" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="595" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
       <c r="A595" s="1">
         <v>45574063867</v>
       </c>
@@ -14290,7 +14298,7 @@
         <v>1785</v>
       </c>
     </row>
-    <row r="596" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="596" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
       <c r="A596" s="1">
         <v>50987392840</v>
       </c>
@@ -14304,7 +14312,7 @@
         <v>1788</v>
       </c>
     </row>
-    <row r="597" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="597" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
       <c r="A597" s="1">
         <v>15009048809</v>
       </c>
@@ -14318,7 +14326,7 @@
         <v>1791</v>
       </c>
     </row>
-    <row r="598" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="598" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
       <c r="A598" s="1">
         <v>2429687674</v>
       </c>
@@ -14332,7 +14340,7 @@
         <v>1794</v>
       </c>
     </row>
-    <row r="599" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="599" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
       <c r="A599" s="1">
         <v>42458291848</v>
       </c>
@@ -14346,7 +14354,7 @@
         <v>1797</v>
       </c>
     </row>
-    <row r="600" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="600" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
       <c r="A600" s="1">
         <v>57364939857</v>
       </c>
@@ -14360,7 +14368,7 @@
         <v>1800</v>
       </c>
     </row>
-    <row r="601" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="601" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
       <c r="A601" s="1">
         <v>21540617882</v>
       </c>
@@ -14374,7 +14382,7 @@
         <v>1803</v>
       </c>
     </row>
-    <row r="602" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="602" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
       <c r="A602" s="1">
         <v>45614968822</v>
       </c>
@@ -14388,7 +14396,7 @@
         <v>1806</v>
       </c>
     </row>
-    <row r="603" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="603" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
       <c r="A603" s="1">
         <v>58533349807</v>
       </c>
@@ -14402,7 +14410,7 @@
         <v>1809</v>
       </c>
     </row>
-    <row r="604" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="604" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
       <c r="A604" s="1">
         <v>27424205846</v>
       </c>
@@ -14416,7 +14424,7 @@
         <v>1812</v>
       </c>
     </row>
-    <row r="605" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="605" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
       <c r="A605" s="1">
         <v>12213421854</v>
       </c>
@@ -14430,7 +14438,7 @@
         <v>1831</v>
       </c>
     </row>
-    <row r="606" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="606" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
       <c r="A606" s="1">
         <v>12946369870</v>
       </c>
@@ -14444,7 +14452,7 @@
         <v>1832</v>
       </c>
     </row>
-    <row r="607" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="607" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
       <c r="A607" s="1">
         <v>41866731874</v>
       </c>
@@ -14458,7 +14466,7 @@
         <v>1833</v>
       </c>
     </row>
-    <row r="608" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="608" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
       <c r="A608" s="1">
         <v>30579044831</v>
       </c>
@@ -14472,7 +14480,7 @@
         <v>1834</v>
       </c>
     </row>
-    <row r="609" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="609" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
       <c r="A609" s="1">
         <v>35504818885</v>
       </c>
@@ -14486,7 +14494,7 @@
         <v>1835</v>
       </c>
     </row>
-    <row r="610" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="610" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
       <c r="A610" s="1">
         <v>41612487840</v>
       </c>
@@ -14500,7 +14508,7 @@
         <v>1836</v>
       </c>
     </row>
-    <row r="611" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="611" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
       <c r="A611" s="1">
         <v>9729839883</v>
       </c>
@@ -14514,7 +14522,7 @@
         <v>1837</v>
       </c>
     </row>
-    <row r="612" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="612" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
       <c r="A612" s="1">
         <v>12208649869</v>
       </c>
@@ -14528,7 +14536,7 @@
         <v>1838</v>
       </c>
     </row>
-    <row r="613" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="613" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
       <c r="A613" s="1">
         <v>5099807402</v>
       </c>
@@ -14542,7 +14550,7 @@
         <v>1839</v>
       </c>
     </row>
-    <row r="614" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="614" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
       <c r="A614" s="1">
         <v>20991362896</v>
       </c>
@@ -14556,7 +14564,7 @@
         <v>1840</v>
       </c>
     </row>
-    <row r="615" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="615" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
       <c r="A615" s="1">
         <v>46762698468</v>
       </c>
@@ -14570,7 +14578,7 @@
         <v>1841</v>
       </c>
     </row>
-    <row r="616" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="616" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
       <c r="A616" s="1">
         <v>28811532833</v>
       </c>
@@ -14584,7 +14592,7 @@
         <v>1842</v>
       </c>
     </row>
-    <row r="617" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="617" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
       <c r="A617" s="1">
         <v>37980635833</v>
       </c>
@@ -14598,7 +14606,7 @@
         <v>1843</v>
       </c>
     </row>
-    <row r="618" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="618" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
       <c r="A618" s="1">
         <v>36697913886</v>
       </c>
@@ -14612,7 +14620,7 @@
         <v>1844</v>
       </c>
     </row>
-    <row r="619" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="619" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
       <c r="A619" s="1">
         <v>9865807831</v>
       </c>
@@ -14626,7 +14634,7 @@
         <v>1845</v>
       </c>
     </row>
-    <row r="620" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="620" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
       <c r="A620" s="1">
         <v>26644532896</v>
       </c>
@@ -14640,7 +14648,7 @@
         <v>1846</v>
       </c>
     </row>
-    <row r="621" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="621" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
       <c r="A621" s="1">
         <v>14474783808</v>
       </c>
@@ -14654,7 +14662,7 @@
         <v>1847</v>
       </c>
     </row>
-    <row r="622" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="622" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
       <c r="A622" s="1">
         <v>23170509845</v>
       </c>
@@ -14669,7 +14677,13 @@
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:D604"/>
+  <autoFilter ref="A1:D622">
+    <filterColumn colId="1">
+      <filters>
+        <filter val="JAQUELINE TOLEDO"/>
+      </filters>
+    </filterColumn>
+  </autoFilter>
   <pageMargins left="0.511811024" right="0.511811024" top="0.78740157499999996" bottom="0.78740157499999996" header="0.31496062000000002" footer="0.31496062000000002"/>
   <pageSetup paperSize="9" orientation="portrait" verticalDpi="0" r:id="rId1"/>
 </worksheet>
